--- a/实体 entity/实体骑乘高度.xlsx
+++ b/实体 entity/实体骑乘高度.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\tree-hole\实体 entity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9894CB85-3316-431F-9DC0-B7BEEF7F2177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A6803B8-BB34-4C37-BAC4-6FB967E29D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1.20.4+测试数据" sheetId="1" r:id="rId1"/>
     <sheet name="1.20.4+组合数据" sheetId="2" r:id="rId2"/>
     <sheet name="1.20.1-测试数据" sheetId="3" r:id="rId3"/>
+    <sheet name="1.20.1-组合数据" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="41">
   <si>
     <t>玩家</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -297,7 +298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -329,6 +330,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -336,7 +343,239 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="30">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -583,32 +822,64 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{ECBC2B67-FC40-458D-A11A-81B8166D56F6}" name="表7" displayName="表7" ref="A2:M36" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{ECBC2B67-FC40-458D-A11A-81B8166D56F6}" name="表7" displayName="表7" ref="A2:M36" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
   <autoFilter ref="A2:M36" xr:uid="{ECBC2B67-FC40-458D-A11A-81B8166D56F6}"/>
   <tableColumns count="13">
-    <tableColumn id="2" xr3:uid="{1A5B9393-745A-40B5-99A3-4C560CC7B2F3}" name="组合编号" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{3B8A2C49-42F1-4867-BF42-2822CDF5E16D}" name="矿车(A)" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{48622B21-7452-4541-82EE-988C88AE65A7}" name="船/竹筏(B)" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{3ABEA036-6A6C-45C5-AA84-DA2D9F697B3D}" name="生物(C)" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{33D96CCA-ACD8-46A8-A267-E02365DAC666}" name="无轨视高" dataDxfId="8">
+    <tableColumn id="2" xr3:uid="{1A5B9393-745A-40B5-99A3-4C560CC7B2F3}" name="组合编号" dataDxfId="27"/>
+    <tableColumn id="15" xr3:uid="{3B8A2C49-42F1-4867-BF42-2822CDF5E16D}" name="矿车(A)" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{48622B21-7452-4541-82EE-988C88AE65A7}" name="船/竹筏(B)" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{3ABEA036-6A6C-45C5-AA84-DA2D9F697B3D}" name="生物(C)" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{33D96CCA-ACD8-46A8-A267-E02365DAC666}" name="无轨视高" dataDxfId="23">
       <calculatedColumnFormula>SUM(J3:L3)+1.62</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{598FE69C-AF3A-46F1-AA80-7BF4B0C020CC}" name="有轨视高" dataDxfId="7">
+    <tableColumn id="9" xr3:uid="{598FE69C-AF3A-46F1-AA80-7BF4B0C020CC}" name="有轨视高" dataDxfId="22">
       <calculatedColumnFormula>SUM(J3:L3)+0.0625+1.62</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F66481C1-D9A2-4C5D-B8A5-F66D7C951622}" name="无轨高度" dataDxfId="6">
-      <calculatedColumnFormula>SUM(J3:M3)</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{F66481C1-D9A2-4C5D-B8A5-F66D7C951622}" name="无轨高度" dataDxfId="21">
+      <calculatedColumnFormula>SUM(J3:L3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{F4B5C6C8-A44A-4E9B-84C0-2F1A0C1E9F82}" name="有轨高度" dataDxfId="5">
+    <tableColumn id="7" xr3:uid="{F4B5C6C8-A44A-4E9B-84C0-2F1A0C1E9F82}" name="有轨高度" dataDxfId="20">
       <calculatedColumnFormula>SUM(J3:L3)+0.0625</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B429005B-3C2A-4B29-BC01-522C8E5715A5}" name="生物窒息高度" dataDxfId="4">
+    <tableColumn id="5" xr3:uid="{B429005B-3C2A-4B29-BC01-522C8E5715A5}" name="生物窒息高度" dataDxfId="19">
       <calculatedColumnFormula>SUM(J3:K3)+M3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{52A6878A-9E03-4079-BD2A-D65774A088C3}" name="矿车(A)2" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{53922683-A52C-4BB1-8910-A8475D84622A}" name="船/竹筏(B)2" dataDxfId="2"/>
-    <tableColumn id="12" xr3:uid="{A29EB1E0-DDBB-4484-A5E5-D5BB3182F6F2}" name="生物(C)2" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{4547FA66-A0F5-4A59-A7D1-7C2E362EC1FF}" name="生物视高" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{52A6878A-9E03-4079-BD2A-D65774A088C3}" name="矿车(A)2" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{53922683-A52C-4BB1-8910-A8475D84622A}" name="船/竹筏(B)2" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{A29EB1E0-DDBB-4484-A5E5-D5BB3182F6F2}" name="生物(C)2" dataDxfId="16"/>
+    <tableColumn id="13" xr3:uid="{4547FA66-A0F5-4A59-A7D1-7C2E362EC1FF}" name="生物视高" dataDxfId="15"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{27945CDA-254B-4AA6-84AD-AE71E61FA140}" name="表7_2" displayName="表7_2" ref="A2:M36" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+  <autoFilter ref="A2:M36" xr:uid="{27945CDA-254B-4AA6-84AD-AE71E61FA140}"/>
+  <tableColumns count="13">
+    <tableColumn id="2" xr3:uid="{E3252128-2842-475D-836E-19597AAACB23}" name="组合编号" dataDxfId="12"/>
+    <tableColumn id="15" xr3:uid="{1A256CD6-F969-4F8A-BF08-782638A053C7}" name="矿车(A)" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{139D25BD-5769-4E1F-A9B3-54F4E782916C}" name="船/竹筏(B)" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{590934DE-6D63-4E32-A2BD-E6D9EEFB943B}" name="生物(C)" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{4205D7C0-92A8-4837-939F-E2DA06176A19}" name="无轨视高" dataDxfId="8">
+      <calculatedColumnFormula>SUM(J3:L3)+1.62</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{67B3BB23-165B-4512-8ECD-5E32DF8E967C}" name="有轨视高" dataDxfId="7">
+      <calculatedColumnFormula>SUM(J3:L3)+0.0625+1.62</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{C1854081-3CCD-47A4-8AC7-A6D4D09865AF}" name="无轨高度" dataDxfId="6">
+      <calculatedColumnFormula>SUM(J3:L3)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{C13933C2-8933-4303-A309-B7187722B680}" name="有轨高度" dataDxfId="5">
+      <calculatedColumnFormula>SUM(J3:L3)+0.0625</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{A1FEBA74-5381-4FEA-B4CA-A6B60B7AF7D5}" name="生物窒息高度" dataDxfId="4">
+      <calculatedColumnFormula>SUM(J3:K3)+M3</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{1664F24A-A49A-43FD-84D6-EA805F9ED691}" name="矿车(A)2" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{2AEE38F2-0B0B-4C64-923E-656338A16C44}" name="船/竹筏(B)2" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{44162916-A597-48D8-ABD1-2FEC989945C2}" name="生物(C)2" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{09CE5323-8E54-4DBC-AA57-EEF2127DE728}" name="生物视高" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1203,25 +1474,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="11" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
       <c r="I1" s="8"/>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
     </row>
@@ -1272,19 +1543,19 @@
       </c>
       <c r="B3" s="2"/>
       <c r="E3" s="3">
-        <f t="shared" ref="E3:E36" si="0">SUM(J3:L3)+1.62</f>
+        <f t="shared" ref="E3" si="0">SUM(J3:L3)+1.62</f>
         <v>1.62</v>
       </c>
       <c r="F3" s="3">
-        <f t="shared" ref="F3:F36" si="1">SUM(J3:L3)+0.0625+1.62</f>
+        <f t="shared" ref="F3" si="1">SUM(J3:L3)+0.0625+1.62</f>
         <v>1.6825000000000001</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" ref="G3:G30" si="2">SUM(J3:L3)</f>
+        <f t="shared" ref="G3" si="2">SUM(J3:L3)</f>
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <f t="shared" ref="H3:H36" si="3">SUM(J3:L3)+0.0625</f>
+        <f t="shared" ref="H3" si="3">SUM(J3:L3)+0.0625</f>
         <v>6.25E-2</v>
       </c>
       <c r="J3" s="6"/>
@@ -1301,19 +1572,19 @@
         <v>12</v>
       </c>
       <c r="E4" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E4:E36" si="4">SUM(J4:L4)+1.62</f>
         <v>1.2075</v>
       </c>
       <c r="F4" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="F4:F36" si="5">SUM(J4:L4)+0.0625+1.62</f>
         <v>1.27</v>
       </c>
       <c r="G4" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="G4:G36" si="6">SUM(J4:L4)</f>
         <v>-0.41249999999999998</v>
       </c>
       <c r="H4" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="H4:H36" si="7">SUM(J4:L4)+0.0625</f>
         <v>-0.35</v>
       </c>
       <c r="J4" s="6">
@@ -1333,19 +1604,19 @@
         <v>18</v>
       </c>
       <c r="E5" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>1.2075</v>
       </c>
       <c r="F5" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>1.27</v>
       </c>
       <c r="G5" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-0.41249999999999998</v>
       </c>
       <c r="H5" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-0.35</v>
       </c>
       <c r="J5" s="6"/>
@@ -1364,19 +1635,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>1.52</v>
       </c>
       <c r="F6" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>1.5825</v>
       </c>
       <c r="G6" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-0.1</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-3.7500000000000006E-2</v>
       </c>
       <c r="J6" s="6"/>
@@ -1391,37 +1662,36 @@
       <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>2</v>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="E7" s="3">
-        <f t="shared" si="0"/>
-        <v>1.8887500000000002</v>
+        <f>SUM(J7:L7)+1.62</f>
+        <v>1.395</v>
       </c>
       <c r="F7" s="3">
-        <f t="shared" si="1"/>
-        <v>1.9512500000000002</v>
+        <f>SUM(J7:L7)+0.0625+1.62</f>
+        <v>1.4575</v>
       </c>
       <c r="G7" s="3">
-        <f t="shared" si="2"/>
-        <v>0.26874999999999999</v>
+        <f>SUM(J7:L7)</f>
+        <v>-0.22499999999999998</v>
       </c>
       <c r="H7" s="3">
-        <f t="shared" si="3"/>
-        <v>0.33124999999999999</v>
-      </c>
-      <c r="I7" s="2">
-        <f t="shared" ref="I7:I14" si="4">SUM(J7:K7)+M7</f>
-        <v>0.76500000000000001</v>
-      </c>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6">
-        <v>0.26874999999999999</v>
-      </c>
-      <c r="M7" s="6">
-        <v>0.76500000000000001</v>
-      </c>
+        <f>SUM(J7:L7)+0.0625</f>
+        <v>-0.16249999999999998</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="K7" s="6">
+        <v>-0.41249999999999998</v>
+      </c>
+      <c r="L7" s="6"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
     </row>
@@ -1429,37 +1699,36 @@
       <c r="A8" s="3">
         <v>5</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>3</v>
+      <c r="B8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="E8" s="3">
-        <f t="shared" si="0"/>
-        <v>2.1325000000000003</v>
+        <f>SUM(J8:L8)+1.62</f>
+        <v>1.7075</v>
       </c>
       <c r="F8" s="3">
-        <f t="shared" si="1"/>
-        <v>2.1950000000000003</v>
+        <f>SUM(J8:L8)+0.0625+1.62</f>
+        <v>1.77</v>
       </c>
       <c r="G8" s="3">
-        <f t="shared" si="2"/>
-        <v>0.51249999999999996</v>
+        <f>SUM(J8:L8)</f>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="H8" s="3">
-        <f t="shared" si="3"/>
-        <v>0.57499999999999996</v>
-      </c>
-      <c r="I8" s="2">
-        <f t="shared" si="4"/>
-        <v>1.425</v>
-      </c>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6">
-        <v>0.51249999999999996</v>
-      </c>
-      <c r="M8" s="6">
-        <v>1.425</v>
-      </c>
+        <f>SUM(J8:L8)+0.0625</f>
+        <v>0.15</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="K8" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="L8" s="6"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
     </row>
@@ -1468,35 +1737,35 @@
         <v>6</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9" s="3">
-        <f t="shared" si="0"/>
-        <v>2.2324999999999999</v>
+        <f t="shared" si="4"/>
+        <v>1.8887500000000002</v>
       </c>
       <c r="F9" s="3">
-        <f t="shared" si="1"/>
-        <v>2.2949999999999999</v>
+        <f t="shared" si="5"/>
+        <v>1.9512500000000002</v>
       </c>
       <c r="G9" s="3">
-        <f t="shared" si="2"/>
-        <v>0.61250000000000004</v>
+        <f t="shared" si="6"/>
+        <v>0.26874999999999999</v>
       </c>
       <c r="H9" s="3">
-        <f t="shared" si="3"/>
-        <v>0.67500000000000004</v>
+        <f t="shared" si="7"/>
+        <v>0.33124999999999999</v>
       </c>
       <c r="I9" s="2">
-        <f t="shared" si="4"/>
-        <v>1.52</v>
+        <f t="shared" ref="I9:I16" si="8">SUM(J9:K9)+M9</f>
+        <v>0.76500000000000001</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6">
-        <v>0.61250000000000004</v>
+        <v>0.26874999999999999</v>
       </c>
       <c r="M9" s="6">
-        <v>1.52</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
@@ -1506,35 +1775,35 @@
         <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E10" s="3">
-        <f t="shared" si="0"/>
-        <v>2.3387500000000001</v>
+        <f t="shared" si="4"/>
+        <v>2.1325000000000003</v>
       </c>
       <c r="F10" s="3">
-        <f t="shared" si="1"/>
-        <v>2.4012500000000001</v>
+        <f t="shared" si="5"/>
+        <v>2.1950000000000003</v>
       </c>
       <c r="G10" s="3">
-        <f t="shared" si="2"/>
-        <v>0.71875</v>
+        <f t="shared" si="6"/>
+        <v>0.51249999999999996</v>
       </c>
       <c r="H10" s="3">
-        <f t="shared" si="3"/>
-        <v>0.78125</v>
+        <f t="shared" si="7"/>
+        <v>0.57499999999999996</v>
       </c>
       <c r="I10" s="2">
-        <f t="shared" si="4"/>
-        <v>1.52</v>
+        <f t="shared" si="8"/>
+        <v>1.425</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6">
-        <v>0.71875</v>
+        <v>0.51249999999999996</v>
       </c>
       <c r="M10" s="6">
-        <v>1.52</v>
+        <v>1.425</v>
       </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
@@ -1544,35 +1813,35 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E11" s="3">
-        <f t="shared" si="0"/>
-        <v>2.39</v>
+        <f t="shared" si="4"/>
+        <v>2.2324999999999999</v>
       </c>
       <c r="F11" s="3">
-        <f t="shared" si="1"/>
-        <v>2.4525000000000001</v>
+        <f t="shared" si="5"/>
+        <v>2.2949999999999999</v>
       </c>
       <c r="G11" s="3">
-        <f t="shared" si="2"/>
-        <v>0.77</v>
+        <f t="shared" si="6"/>
+        <v>0.61250000000000004</v>
       </c>
       <c r="H11" s="3">
-        <f t="shared" si="3"/>
-        <v>0.83250000000000002</v>
+        <f t="shared" si="7"/>
+        <v>0.67500000000000004</v>
       </c>
       <c r="I11" s="2">
-        <f t="shared" si="4"/>
-        <v>1.7765</v>
+        <f t="shared" si="8"/>
+        <v>1.52</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6">
-        <v>0.77</v>
+        <v>0.61250000000000004</v>
       </c>
       <c r="M11" s="6">
-        <v>1.7765</v>
+        <v>1.52</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
@@ -1582,32 +1851,32 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" si="0"/>
-        <v>2.4637500000000001</v>
+        <f t="shared" si="4"/>
+        <v>2.3387500000000001</v>
       </c>
       <c r="F12" s="3">
-        <f t="shared" si="1"/>
-        <v>2.5262500000000001</v>
+        <f t="shared" si="5"/>
+        <v>2.4012500000000001</v>
       </c>
       <c r="G12" s="3">
-        <f t="shared" si="2"/>
-        <v>0.84375</v>
+        <f t="shared" si="6"/>
+        <v>0.71875</v>
       </c>
       <c r="H12" s="3">
-        <f t="shared" si="3"/>
-        <v>0.90625</v>
+        <f t="shared" si="7"/>
+        <v>0.78125</v>
       </c>
       <c r="I12" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1.52</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6">
-        <v>0.84375</v>
+        <v>0.71875</v>
       </c>
       <c r="M12" s="6">
         <v>1.52</v>
@@ -1620,35 +1889,35 @@
         <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E13" s="3">
-        <f t="shared" si="0"/>
-        <v>2.72</v>
+        <f t="shared" si="4"/>
+        <v>2.39</v>
       </c>
       <c r="F13" s="3">
-        <f t="shared" si="1"/>
-        <v>2.7825000000000002</v>
+        <f t="shared" si="5"/>
+        <v>2.4525000000000001</v>
       </c>
       <c r="G13" s="3">
-        <f t="shared" si="2"/>
-        <v>1.1000000000000001</v>
+        <f t="shared" si="6"/>
+        <v>0.77</v>
       </c>
       <c r="H13" s="3">
-        <f t="shared" si="3"/>
-        <v>1.1625000000000001</v>
+        <f t="shared" si="7"/>
+        <v>0.83250000000000002</v>
       </c>
       <c r="I13" s="2">
-        <f t="shared" si="4"/>
-        <v>1.4450000000000001</v>
+        <f t="shared" si="8"/>
+        <v>1.7765</v>
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
       <c r="L13" s="6">
-        <v>1.1000000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="M13" s="6">
-        <v>1.4450000000000001</v>
+        <v>1.7765</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
@@ -1658,35 +1927,35 @@
         <v>11</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" s="3">
-        <f t="shared" si="0"/>
-        <v>3.02</v>
+        <f t="shared" si="4"/>
+        <v>2.4637500000000001</v>
       </c>
       <c r="F14" s="3">
-        <f t="shared" si="1"/>
-        <v>3.0825</v>
+        <f t="shared" si="5"/>
+        <v>2.5262500000000001</v>
       </c>
       <c r="G14" s="3">
-        <f t="shared" si="2"/>
-        <v>1.4</v>
+        <f t="shared" si="6"/>
+        <v>0.84375</v>
       </c>
       <c r="H14" s="3">
-        <f t="shared" si="3"/>
-        <v>1.4624999999999999</v>
+        <f t="shared" si="7"/>
+        <v>0.90625</v>
       </c>
       <c r="I14" s="2">
-        <f t="shared" si="4"/>
-        <v>2.2749999999999999</v>
+        <f t="shared" si="8"/>
+        <v>1.52</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
       <c r="L14" s="6">
-        <v>1.4</v>
+        <v>0.84375</v>
       </c>
       <c r="M14" s="6">
-        <v>2.2749999999999999</v>
+        <v>1.52</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
@@ -1695,36 +1964,37 @@
       <c r="A15" s="3">
         <v>12</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>18</v>
+      <c r="D15" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="E15" s="3">
-        <f t="shared" si="0"/>
-        <v>1.395</v>
+        <f t="shared" si="4"/>
+        <v>2.72</v>
       </c>
       <c r="F15" s="3">
-        <f t="shared" si="1"/>
-        <v>1.4575</v>
+        <f t="shared" si="5"/>
+        <v>2.7825000000000002</v>
       </c>
       <c r="G15" s="3">
-        <f t="shared" si="2"/>
-        <v>-0.22499999999999998</v>
+        <f t="shared" si="6"/>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H15" s="3">
-        <f t="shared" si="3"/>
-        <v>-0.16249999999999998</v>
-      </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="6">
-        <v>0.1875</v>
-      </c>
-      <c r="K15" s="6">
-        <v>-0.41249999999999998</v>
-      </c>
-      <c r="L15" s="6"/>
+        <f t="shared" si="7"/>
+        <v>1.1625000000000001</v>
+      </c>
+      <c r="I15" s="2">
+        <f t="shared" si="8"/>
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M15" s="6">
+        <v>1.4450000000000001</v>
+      </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
     </row>
@@ -1732,36 +2002,37 @@
       <c r="A16" s="3">
         <v>13</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>1</v>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E16" s="3">
-        <f t="shared" si="0"/>
-        <v>1.7075</v>
+        <f t="shared" si="4"/>
+        <v>3.02</v>
       </c>
       <c r="F16" s="3">
-        <f t="shared" si="1"/>
-        <v>1.77</v>
+        <f t="shared" si="5"/>
+        <v>3.0825</v>
       </c>
       <c r="G16" s="3">
-        <f t="shared" si="2"/>
-        <v>8.7499999999999994E-2</v>
+        <f t="shared" si="6"/>
+        <v>1.4</v>
       </c>
       <c r="H16" s="3">
-        <f t="shared" si="3"/>
-        <v>0.15</v>
-      </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="6">
-        <v>0.1875</v>
-      </c>
-      <c r="K16" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="L16" s="6"/>
+        <f t="shared" si="7"/>
+        <v>1.4624999999999999</v>
+      </c>
+      <c r="I16" s="2">
+        <f t="shared" si="8"/>
+        <v>2.2749999999999999</v>
+      </c>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="M16" s="6">
+        <v>2.2749999999999999</v>
+      </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
     </row>
@@ -1776,23 +2047,23 @@
         <v>2</v>
       </c>
       <c r="E17" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.0762499999999999</v>
       </c>
       <c r="F17" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.1387499999999999</v>
       </c>
       <c r="G17" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0.45624999999999999</v>
       </c>
       <c r="H17" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.51875000000000004</v>
       </c>
       <c r="I17" s="2">
-        <f t="shared" ref="I17:I36" si="5">SUM(J17:K17)+M17</f>
+        <f t="shared" ref="I17:I36" si="9">SUM(J17:K17)+M17</f>
         <v>0.95250000000000001</v>
       </c>
       <c r="J17" s="6">
@@ -1819,23 +2090,23 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.3200000000000003</v>
       </c>
       <c r="F18" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.3825000000000003</v>
       </c>
       <c r="G18" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0.7</v>
       </c>
       <c r="H18" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.76249999999999996</v>
       </c>
       <c r="I18" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.6125</v>
       </c>
       <c r="J18" s="6">
@@ -1862,23 +2133,23 @@
         <v>4</v>
       </c>
       <c r="E19" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.42</v>
       </c>
       <c r="F19" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.4824999999999999</v>
       </c>
       <c r="G19" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0.8</v>
       </c>
       <c r="H19" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.86250000000000004</v>
       </c>
       <c r="I19" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.7075</v>
       </c>
       <c r="J19" s="6">
@@ -1905,23 +2176,23 @@
         <v>5</v>
       </c>
       <c r="E20" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>1.3387500000000001</v>
       </c>
       <c r="F20" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>1.4012500000000001</v>
       </c>
       <c r="G20" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-0.28125</v>
       </c>
       <c r="H20" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-0.21875</v>
       </c>
       <c r="I20" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.52</v>
       </c>
       <c r="J20" s="6">
@@ -1948,23 +2219,23 @@
         <v>6</v>
       </c>
       <c r="E21" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>1.3900000000000001</v>
       </c>
       <c r="F21" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>1.4525000000000001</v>
       </c>
       <c r="G21" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-0.22999999999999998</v>
       </c>
       <c r="H21" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-0.16749999999999998</v>
       </c>
       <c r="I21" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.77649999999999997</v>
       </c>
       <c r="J21" s="6">
@@ -1991,23 +2262,23 @@
         <v>7</v>
       </c>
       <c r="E22" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.6512500000000001</v>
       </c>
       <c r="F22" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.7137500000000001</v>
       </c>
       <c r="G22" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.03125</v>
       </c>
       <c r="H22" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.09375</v>
       </c>
       <c r="I22" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.7075</v>
       </c>
       <c r="J22" s="6">
@@ -2034,23 +2305,23 @@
         <v>16</v>
       </c>
       <c r="E23" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.97</v>
       </c>
       <c r="F23" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>3.0325000000000002</v>
       </c>
       <c r="G23" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.35</v>
       </c>
       <c r="H23" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.4125000000000001</v>
       </c>
       <c r="I23" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.6950000000000001</v>
       </c>
       <c r="J23" s="6">
@@ -2077,23 +2348,23 @@
         <v>8</v>
       </c>
       <c r="E24" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.2075</v>
       </c>
       <c r="F24" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>3.27</v>
       </c>
       <c r="G24" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.5874999999999999</v>
       </c>
       <c r="H24" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.65</v>
       </c>
       <c r="I24" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.4624999999999999</v>
       </c>
       <c r="J24" s="6">
@@ -2120,23 +2391,23 @@
         <v>2</v>
       </c>
       <c r="E25" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.0762499999999999</v>
       </c>
       <c r="F25" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.1387499999999999</v>
       </c>
       <c r="G25" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0.45624999999999999</v>
       </c>
       <c r="H25" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.51875000000000004</v>
       </c>
       <c r="I25" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.95250000000000001</v>
       </c>
       <c r="J25" s="6"/>
@@ -2163,23 +2434,23 @@
         <v>21</v>
       </c>
       <c r="E26" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.5775000000000001</v>
       </c>
       <c r="F26" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.64</v>
       </c>
       <c r="G26" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0.95750000000000002</v>
       </c>
       <c r="H26" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.02</v>
       </c>
       <c r="I26" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.964</v>
       </c>
       <c r="J26" s="6"/>
@@ -2206,23 +2477,23 @@
         <v>20</v>
       </c>
       <c r="E27" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.9075000000000002</v>
       </c>
       <c r="F27" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.97</v>
       </c>
       <c r="G27" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.2875000000000001</v>
       </c>
       <c r="H27" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.35</v>
       </c>
       <c r="I27" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.6325000000000001</v>
       </c>
       <c r="J27" s="6"/>
@@ -2249,23 +2520,23 @@
         <v>2</v>
       </c>
       <c r="E28" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.3887499999999999</v>
       </c>
       <c r="F28" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.4512499999999999</v>
       </c>
       <c r="G28" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0.76875000000000004</v>
       </c>
       <c r="H28" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.83125000000000004</v>
       </c>
       <c r="I28" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.2650000000000001</v>
       </c>
       <c r="J28" s="6"/>
@@ -2292,23 +2563,23 @@
         <v>6</v>
       </c>
       <c r="E29" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.89</v>
       </c>
       <c r="F29" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.9525000000000001</v>
       </c>
       <c r="G29" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.27</v>
       </c>
       <c r="H29" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.3325</v>
       </c>
       <c r="I29" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.2765</v>
       </c>
       <c r="J29" s="6"/>
@@ -2335,23 +2606,23 @@
         <v>20</v>
       </c>
       <c r="E30" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.22</v>
       </c>
       <c r="F30" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>3.2825000000000002</v>
       </c>
       <c r="G30" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.6</v>
       </c>
       <c r="H30" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.6625000000000001</v>
       </c>
       <c r="I30" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.9450000000000001</v>
       </c>
       <c r="J30" s="6"/>
@@ -2381,23 +2652,23 @@
         <v>2</v>
       </c>
       <c r="E31" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.2637499999999999</v>
       </c>
       <c r="F31" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.3262499999999999</v>
       </c>
       <c r="G31" s="3">
-        <f t="shared" ref="G31:G36" si="6">SUM(J31:M31)</f>
-        <v>1.4087499999999999</v>
+        <f t="shared" si="6"/>
+        <v>0.64375000000000004</v>
       </c>
       <c r="H31" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.70625000000000004</v>
       </c>
       <c r="I31" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.1400000000000001</v>
       </c>
       <c r="J31" s="6">
@@ -2429,23 +2700,23 @@
         <v>21</v>
       </c>
       <c r="E32" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.7650000000000001</v>
       </c>
       <c r="F32" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.8275000000000001</v>
       </c>
       <c r="G32" s="3">
         <f t="shared" si="6"/>
-        <v>2.9215</v>
+        <v>1.145</v>
       </c>
       <c r="H32" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.2075</v>
       </c>
       <c r="I32" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.1515</v>
       </c>
       <c r="J32" s="6">
@@ -2477,23 +2748,23 @@
         <v>20</v>
       </c>
       <c r="E33" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.0950000000000002</v>
       </c>
       <c r="F33" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>3.1575000000000002</v>
       </c>
       <c r="G33" s="3">
         <f t="shared" si="6"/>
-        <v>2.92</v>
+        <v>1.4750000000000001</v>
       </c>
       <c r="H33" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.5375000000000001</v>
       </c>
       <c r="I33" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.82</v>
       </c>
       <c r="J33" s="6">
@@ -2525,23 +2796,23 @@
         <v>2</v>
       </c>
       <c r="E34" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.5762499999999999</v>
       </c>
       <c r="F34" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.6387499999999999</v>
       </c>
       <c r="G34" s="3">
         <f t="shared" si="6"/>
-        <v>1.7212499999999999</v>
+        <v>0.95625000000000004</v>
       </c>
       <c r="H34" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.01875</v>
       </c>
       <c r="I34" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.4525000000000001</v>
       </c>
       <c r="J34" s="6">
@@ -2573,23 +2844,23 @@
         <v>6</v>
       </c>
       <c r="E35" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.0775000000000001</v>
       </c>
       <c r="F35" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>3.14</v>
       </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
-        <v>3.234</v>
+        <v>1.4575</v>
       </c>
       <c r="H35" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.52</v>
       </c>
       <c r="I35" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.464</v>
       </c>
       <c r="J35" s="6">
@@ -2621,23 +2892,23 @@
         <v>20</v>
       </c>
       <c r="E36" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.4075000000000002</v>
       </c>
       <c r="F36" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>3.47</v>
       </c>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
-        <v>3.2324999999999999</v>
+        <v>1.7875000000000001</v>
       </c>
       <c r="H36" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.85</v>
       </c>
       <c r="I36" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.1325000000000003</v>
       </c>
       <c r="J36" s="6">
@@ -2671,11 +2942,1820 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEB9D88C-9594-4ED7-93DA-80DA60D28A9A}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1.62</v>
+      </c>
+      <c r="D3" s="2">
+        <f>C3*16</f>
+        <v>25.92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2">
+        <v>6.25E-2</v>
+      </c>
+      <c r="D4" s="2">
+        <f t="shared" ref="D4:D24" si="0">C4*16</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>-0.35</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="0"/>
+        <v>-5.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>-0.35</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="0"/>
+        <v>-5.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="0"/>
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="0"/>
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="0"/>
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="D11" s="2">
+        <f t="shared" si="0"/>
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.66249999999999998</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" si="0"/>
+        <v>12.352</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="0"/>
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" si="0"/>
+        <v>18.559999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1.425</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="0"/>
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="D18" s="2">
+        <f t="shared" si="0"/>
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="D20" s="2">
+        <f t="shared" si="0"/>
+        <v>6.24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D22" s="2">
+        <f t="shared" si="0"/>
+        <v>2.2400000000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="0"/>
+        <v>2.2400000000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="0"/>
+        <v>2.2400000000000002</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3807DD25-8EFF-4D65-BFF6-A690D0D26684}">
+  <dimension ref="A1:O36"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.58203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.4140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.9140625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+    </row>
+    <row r="2" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="E3" s="3">
+        <f t="shared" ref="E3:E36" si="0">SUM(J3:L3)+1.62</f>
+        <v>1.62</v>
+      </c>
+      <c r="F3" s="3">
+        <f t="shared" ref="F3:F36" si="1">SUM(J3:L3)+0.0625+1.62</f>
+        <v>1.6825000000000001</v>
+      </c>
+      <c r="G3" s="3">
+        <f t="shared" ref="G3:G30" si="2">SUM(J3:L3)</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <f t="shared" ref="H3:H36" si="3">SUM(J3:L3)+0.0625</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="3">
+        <f t="shared" ref="E4:E36" si="4">SUM(J4:L4)+1.62</f>
+        <v>1.27</v>
+      </c>
+      <c r="F4" s="3">
+        <f t="shared" ref="F4:F36" si="5">SUM(J4:L4)+0.0625+1.62</f>
+        <v>1.3325</v>
+      </c>
+      <c r="G4" s="3">
+        <f t="shared" ref="G4:G36" si="6">SUM(J4:L4)</f>
+        <v>-0.35</v>
+      </c>
+      <c r="H4" s="3">
+        <f t="shared" ref="H4:H36" si="7">SUM(J4:L4)+0.0625</f>
+        <v>-0.28749999999999998</v>
+      </c>
+      <c r="J4" s="6">
+        <v>-0.35</v>
+      </c>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3">
+        <f t="shared" si="4"/>
+        <v>1.27</v>
+      </c>
+      <c r="F5" s="3">
+        <f t="shared" si="5"/>
+        <v>1.3325</v>
+      </c>
+      <c r="G5" s="3">
+        <f t="shared" si="6"/>
+        <v>-0.35</v>
+      </c>
+      <c r="H5" s="3">
+        <f t="shared" si="7"/>
+        <v>-0.28749999999999998</v>
+      </c>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6">
+        <v>-0.35</v>
+      </c>
+      <c r="L5" s="6"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <f t="shared" si="4"/>
+        <v>1.52</v>
+      </c>
+      <c r="F6" s="3">
+        <f t="shared" si="5"/>
+        <v>1.5825</v>
+      </c>
+      <c r="G6" s="3">
+        <f t="shared" si="6"/>
+        <v>-0.1</v>
+      </c>
+      <c r="H6" s="3">
+        <f t="shared" si="7"/>
+        <v>-3.7500000000000006E-2</v>
+      </c>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="L6" s="6"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="3">
+        <f t="shared" si="4"/>
+        <v>1.27</v>
+      </c>
+      <c r="F7" s="3">
+        <f t="shared" si="5"/>
+        <v>1.3325</v>
+      </c>
+      <c r="G7" s="3">
+        <f t="shared" si="6"/>
+        <v>-0.35</v>
+      </c>
+      <c r="H7" s="3">
+        <f t="shared" si="7"/>
+        <v>-0.28749999999999998</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="6">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6">
+        <v>-0.35</v>
+      </c>
+      <c r="L7" s="6"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>13</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" si="4"/>
+        <v>1.52</v>
+      </c>
+      <c r="F8" s="3">
+        <f t="shared" si="5"/>
+        <v>1.5825</v>
+      </c>
+      <c r="G8" s="3">
+        <f t="shared" si="6"/>
+        <v>-0.1</v>
+      </c>
+      <c r="H8" s="3">
+        <f t="shared" si="7"/>
+        <v>-3.7500000000000006E-2</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="6">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="L8" s="6"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3">
+        <f t="shared" si="4"/>
+        <v>1.9450000000000001</v>
+      </c>
+      <c r="F9" s="3">
+        <f t="shared" si="5"/>
+        <v>2.0075000000000003</v>
+      </c>
+      <c r="G9" s="3">
+        <f t="shared" si="6"/>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="H9" s="3">
+        <f t="shared" si="7"/>
+        <v>0.38750000000000001</v>
+      </c>
+      <c r="I9" s="2">
+        <f t="shared" ref="I9:I16" si="8">SUM(J9:K9)+M9</f>
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M9" s="6">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
+        <f t="shared" si="4"/>
+        <v>2.145</v>
+      </c>
+      <c r="F10" s="3">
+        <f t="shared" si="5"/>
+        <v>2.2075</v>
+      </c>
+      <c r="G10" s="3">
+        <f t="shared" si="6"/>
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="H10" s="3">
+        <f t="shared" si="7"/>
+        <v>0.58750000000000002</v>
+      </c>
+      <c r="I10" s="2">
+        <f t="shared" si="8"/>
+        <v>1.425</v>
+      </c>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="M10" s="6">
+        <v>1.425</v>
+      </c>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>6</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="3">
+        <f t="shared" si="4"/>
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="F11" s="3">
+        <f t="shared" si="5"/>
+        <v>2.2825000000000002</v>
+      </c>
+      <c r="G11" s="3">
+        <f t="shared" si="6"/>
+        <v>0.6</v>
+      </c>
+      <c r="H11" s="3">
+        <f t="shared" si="7"/>
+        <v>0.66249999999999998</v>
+      </c>
+      <c r="I11" s="2">
+        <f t="shared" si="8"/>
+        <v>1.52</v>
+      </c>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="M11" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>7</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="4"/>
+        <v>2.2825000000000002</v>
+      </c>
+      <c r="F12" s="3">
+        <f t="shared" si="5"/>
+        <v>2.3450000000000002</v>
+      </c>
+      <c r="G12" s="3">
+        <f t="shared" si="6"/>
+        <v>0.66249999999999998</v>
+      </c>
+      <c r="H12" s="3">
+        <f t="shared" si="7"/>
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="I12" s="2">
+        <f t="shared" si="8"/>
+        <v>1.52</v>
+      </c>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6">
+        <v>0.66249999999999998</v>
+      </c>
+      <c r="M12" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="4"/>
+        <v>2.3920000000000003</v>
+      </c>
+      <c r="F13" s="3">
+        <f t="shared" si="5"/>
+        <v>2.4545000000000003</v>
+      </c>
+      <c r="G13" s="3">
+        <f t="shared" si="6"/>
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="H13" s="3">
+        <f t="shared" si="7"/>
+        <v>0.83450000000000002</v>
+      </c>
+      <c r="I13" s="2">
+        <f t="shared" si="8"/>
+        <v>1.7765</v>
+      </c>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="M13" s="6">
+        <v>1.7765</v>
+      </c>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="3">
+        <f t="shared" si="4"/>
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="F14" s="3">
+        <f t="shared" si="5"/>
+        <v>2.5325000000000002</v>
+      </c>
+      <c r="G14" s="3">
+        <f t="shared" si="6"/>
+        <v>0.85</v>
+      </c>
+      <c r="H14" s="3">
+        <f t="shared" si="7"/>
+        <v>0.91249999999999998</v>
+      </c>
+      <c r="I14" s="2">
+        <f t="shared" si="8"/>
+        <v>1.52</v>
+      </c>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="M14" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="3">
+        <f t="shared" si="4"/>
+        <v>2.7800000000000002</v>
+      </c>
+      <c r="F15" s="3">
+        <f t="shared" si="5"/>
+        <v>2.8425000000000002</v>
+      </c>
+      <c r="G15" s="3">
+        <f t="shared" si="6"/>
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="H15" s="3">
+        <f t="shared" si="7"/>
+        <v>1.2224999999999999</v>
+      </c>
+      <c r="I15" s="2">
+        <f t="shared" si="8"/>
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="M15" s="6">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>11</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" si="4"/>
+        <v>3.0449999999999999</v>
+      </c>
+      <c r="F16" s="3">
+        <f t="shared" si="5"/>
+        <v>3.1074999999999999</v>
+      </c>
+      <c r="G16" s="3">
+        <f t="shared" si="6"/>
+        <v>1.425</v>
+      </c>
+      <c r="H16" s="3">
+        <f t="shared" si="7"/>
+        <v>1.4875</v>
+      </c>
+      <c r="I16" s="2">
+        <f t="shared" si="8"/>
+        <v>2.2749999999999999</v>
+      </c>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6">
+        <v>1.425</v>
+      </c>
+      <c r="M16" s="6">
+        <v>2.2749999999999999</v>
+      </c>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" si="4"/>
+        <v>2.085</v>
+      </c>
+      <c r="F17" s="3">
+        <f t="shared" si="5"/>
+        <v>2.1475</v>
+      </c>
+      <c r="G17" s="3">
+        <f t="shared" si="6"/>
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="H17" s="3">
+        <f t="shared" si="7"/>
+        <v>0.52750000000000008</v>
+      </c>
+      <c r="I17" s="2">
+        <f t="shared" ref="I17:I36" si="9">SUM(J17:K17)+M17</f>
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="J17" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M17" s="6">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" si="4"/>
+        <v>2.2850000000000001</v>
+      </c>
+      <c r="F18" s="3">
+        <f t="shared" si="5"/>
+        <v>2.3475000000000001</v>
+      </c>
+      <c r="G18" s="3">
+        <f t="shared" si="6"/>
+        <v>0.66500000000000004</v>
+      </c>
+      <c r="H18" s="3">
+        <f t="shared" si="7"/>
+        <v>0.72750000000000004</v>
+      </c>
+      <c r="I18" s="2">
+        <f t="shared" si="9"/>
+        <v>1.5649999999999999</v>
+      </c>
+      <c r="J18" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="M18" s="6">
+        <v>1.425</v>
+      </c>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" si="4"/>
+        <v>2.3600000000000003</v>
+      </c>
+      <c r="F19" s="3">
+        <f t="shared" si="5"/>
+        <v>2.4225000000000003</v>
+      </c>
+      <c r="G19" s="3">
+        <f t="shared" si="6"/>
+        <v>0.74</v>
+      </c>
+      <c r="H19" s="3">
+        <f t="shared" si="7"/>
+        <v>0.80249999999999999</v>
+      </c>
+      <c r="I19" s="2">
+        <f t="shared" si="9"/>
+        <v>1.6600000000000001</v>
+      </c>
+      <c r="J19" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="M19" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" si="4"/>
+        <v>2.4225000000000003</v>
+      </c>
+      <c r="F20" s="3">
+        <f t="shared" si="5"/>
+        <v>2.4850000000000003</v>
+      </c>
+      <c r="G20" s="3">
+        <f t="shared" si="6"/>
+        <v>0.80249999999999999</v>
+      </c>
+      <c r="H20" s="3">
+        <f t="shared" si="7"/>
+        <v>0.86499999999999999</v>
+      </c>
+      <c r="I20" s="2">
+        <f t="shared" si="9"/>
+        <v>1.6600000000000001</v>
+      </c>
+      <c r="J20" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6">
+        <v>0.66249999999999998</v>
+      </c>
+      <c r="M20" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="3">
+        <f t="shared" si="4"/>
+        <v>2.532</v>
+      </c>
+      <c r="F21" s="3">
+        <f t="shared" si="5"/>
+        <v>2.5945</v>
+      </c>
+      <c r="G21" s="3">
+        <f t="shared" si="6"/>
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="H21" s="3">
+        <f t="shared" si="7"/>
+        <v>0.97450000000000003</v>
+      </c>
+      <c r="I21" s="2">
+        <f t="shared" si="9"/>
+        <v>1.9165000000000001</v>
+      </c>
+      <c r="J21" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="M21" s="6">
+        <v>1.7765</v>
+      </c>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="3">
+        <f t="shared" si="4"/>
+        <v>2.6100000000000003</v>
+      </c>
+      <c r="F22" s="3">
+        <f t="shared" si="5"/>
+        <v>2.6725000000000003</v>
+      </c>
+      <c r="G22" s="3">
+        <f t="shared" si="6"/>
+        <v>0.99</v>
+      </c>
+      <c r="H22" s="3">
+        <f t="shared" si="7"/>
+        <v>1.0525</v>
+      </c>
+      <c r="I22" s="2">
+        <f t="shared" si="9"/>
+        <v>1.6600000000000001</v>
+      </c>
+      <c r="J22" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="M22" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="3">
+        <f t="shared" si="4"/>
+        <v>2.92</v>
+      </c>
+      <c r="F23" s="3">
+        <f t="shared" si="5"/>
+        <v>2.9824999999999999</v>
+      </c>
+      <c r="G23" s="3">
+        <f t="shared" si="6"/>
+        <v>1.2999999999999998</v>
+      </c>
+      <c r="H23" s="3">
+        <f t="shared" si="7"/>
+        <v>1.3624999999999998</v>
+      </c>
+      <c r="I23" s="2">
+        <f t="shared" si="9"/>
+        <v>1.585</v>
+      </c>
+      <c r="J23" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="M23" s="6">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3">
+        <f t="shared" si="4"/>
+        <v>3.1850000000000001</v>
+      </c>
+      <c r="F24" s="3">
+        <f t="shared" si="5"/>
+        <v>3.2475000000000001</v>
+      </c>
+      <c r="G24" s="3">
+        <f t="shared" si="6"/>
+        <v>1.5649999999999999</v>
+      </c>
+      <c r="H24" s="3">
+        <f t="shared" si="7"/>
+        <v>1.6274999999999999</v>
+      </c>
+      <c r="I24" s="2">
+        <f t="shared" si="9"/>
+        <v>2.415</v>
+      </c>
+      <c r="J24" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6">
+        <v>1.425</v>
+      </c>
+      <c r="M24" s="6">
+        <v>2.2749999999999999</v>
+      </c>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <v>22</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" si="4"/>
+        <v>2.085</v>
+      </c>
+      <c r="F25" s="3">
+        <f t="shared" si="5"/>
+        <v>2.1475</v>
+      </c>
+      <c r="G25" s="3">
+        <f t="shared" si="6"/>
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="H25" s="3">
+        <f t="shared" si="7"/>
+        <v>0.52750000000000008</v>
+      </c>
+      <c r="I25" s="2">
+        <f t="shared" si="9"/>
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L25" s="6">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M25" s="6">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>23</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="3">
+        <f t="shared" si="4"/>
+        <v>2.532</v>
+      </c>
+      <c r="F26" s="3">
+        <f t="shared" si="5"/>
+        <v>2.5945</v>
+      </c>
+      <c r="G26" s="3">
+        <f t="shared" si="6"/>
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="H26" s="3">
+        <f t="shared" si="7"/>
+        <v>0.97450000000000003</v>
+      </c>
+      <c r="I26" s="2">
+        <f t="shared" si="9"/>
+        <v>1.9165000000000001</v>
+      </c>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L26" s="6">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="M26" s="6">
+        <v>1.7765</v>
+      </c>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>24</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="3">
+        <f t="shared" si="4"/>
+        <v>2.92</v>
+      </c>
+      <c r="F27" s="3">
+        <f t="shared" si="5"/>
+        <v>2.9824999999999999</v>
+      </c>
+      <c r="G27" s="3">
+        <f t="shared" si="6"/>
+        <v>1.2999999999999998</v>
+      </c>
+      <c r="H27" s="3">
+        <f t="shared" si="7"/>
+        <v>1.3624999999999998</v>
+      </c>
+      <c r="I27" s="2">
+        <f t="shared" si="9"/>
+        <v>1.585</v>
+      </c>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L27" s="6">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="M27" s="6">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>25</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" si="4"/>
+        <v>2.335</v>
+      </c>
+      <c r="F28" s="3">
+        <f t="shared" si="5"/>
+        <v>2.3975</v>
+      </c>
+      <c r="G28" s="3">
+        <f t="shared" si="6"/>
+        <v>0.71500000000000008</v>
+      </c>
+      <c r="H28" s="3">
+        <f t="shared" si="7"/>
+        <v>0.77750000000000008</v>
+      </c>
+      <c r="I28" s="2">
+        <f t="shared" si="9"/>
+        <v>1.155</v>
+      </c>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="L28" s="6">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M28" s="6">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>26</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" s="3">
+        <f t="shared" si="4"/>
+        <v>2.782</v>
+      </c>
+      <c r="F29" s="3">
+        <f t="shared" si="5"/>
+        <v>2.8445</v>
+      </c>
+      <c r="G29" s="3">
+        <f t="shared" si="6"/>
+        <v>1.1619999999999999</v>
+      </c>
+      <c r="H29" s="3">
+        <f t="shared" si="7"/>
+        <v>1.2244999999999999</v>
+      </c>
+      <c r="I29" s="2">
+        <f t="shared" si="9"/>
+        <v>2.1665000000000001</v>
+      </c>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="L29" s="6">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="M29" s="6">
+        <v>1.7765</v>
+      </c>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <v>27</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="3">
+        <f t="shared" si="4"/>
+        <v>3.17</v>
+      </c>
+      <c r="F30" s="3">
+        <f t="shared" si="5"/>
+        <v>3.2324999999999999</v>
+      </c>
+      <c r="G30" s="3">
+        <f t="shared" si="6"/>
+        <v>1.5499999999999998</v>
+      </c>
+      <c r="H30" s="3">
+        <f t="shared" si="7"/>
+        <v>1.6124999999999998</v>
+      </c>
+      <c r="I30" s="2">
+        <f t="shared" si="9"/>
+        <v>1.835</v>
+      </c>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="L30" s="6">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="M30" s="6">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3">
+        <f t="shared" si="4"/>
+        <v>2.085</v>
+      </c>
+      <c r="F31" s="3">
+        <f t="shared" si="5"/>
+        <v>2.1475</v>
+      </c>
+      <c r="G31" s="3">
+        <f t="shared" si="6"/>
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="H31" s="3">
+        <f t="shared" si="7"/>
+        <v>0.52750000000000008</v>
+      </c>
+      <c r="I31" s="2">
+        <f t="shared" si="9"/>
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="J31" s="6">
+        <v>0</v>
+      </c>
+      <c r="K31" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L31" s="6">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M31" s="6">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <v>29</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" s="3">
+        <f t="shared" si="4"/>
+        <v>2.532</v>
+      </c>
+      <c r="F32" s="3">
+        <f t="shared" si="5"/>
+        <v>2.5945</v>
+      </c>
+      <c r="G32" s="3">
+        <f t="shared" si="6"/>
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="H32" s="3">
+        <f t="shared" si="7"/>
+        <v>0.97450000000000003</v>
+      </c>
+      <c r="I32" s="2">
+        <f t="shared" si="9"/>
+        <v>1.9165000000000001</v>
+      </c>
+      <c r="J32" s="6">
+        <v>0</v>
+      </c>
+      <c r="K32" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L32" s="6">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="M32" s="6">
+        <v>1.7765</v>
+      </c>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <v>30</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="3">
+        <f t="shared" si="4"/>
+        <v>2.92</v>
+      </c>
+      <c r="F33" s="3">
+        <f t="shared" si="5"/>
+        <v>2.9824999999999999</v>
+      </c>
+      <c r="G33" s="3">
+        <f t="shared" si="6"/>
+        <v>1.2999999999999998</v>
+      </c>
+      <c r="H33" s="3">
+        <f t="shared" si="7"/>
+        <v>1.3624999999999998</v>
+      </c>
+      <c r="I33" s="2">
+        <f t="shared" si="9"/>
+        <v>1.585</v>
+      </c>
+      <c r="J33" s="6">
+        <v>0</v>
+      </c>
+      <c r="K33" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L33" s="6">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="M33" s="6">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <v>31</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E34" s="3">
+        <f t="shared" si="4"/>
+        <v>2.335</v>
+      </c>
+      <c r="F34" s="3">
+        <f t="shared" si="5"/>
+        <v>2.3975</v>
+      </c>
+      <c r="G34" s="3">
+        <f t="shared" si="6"/>
+        <v>0.71500000000000008</v>
+      </c>
+      <c r="H34" s="3">
+        <f t="shared" si="7"/>
+        <v>0.77750000000000008</v>
+      </c>
+      <c r="I34" s="2">
+        <f t="shared" si="9"/>
+        <v>1.155</v>
+      </c>
+      <c r="J34" s="6">
+        <v>0</v>
+      </c>
+      <c r="K34" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="L34" s="6">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M34" s="6">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <v>32</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" s="3">
+        <f t="shared" si="4"/>
+        <v>2.782</v>
+      </c>
+      <c r="F35" s="3">
+        <f t="shared" si="5"/>
+        <v>2.8445</v>
+      </c>
+      <c r="G35" s="3">
+        <f t="shared" si="6"/>
+        <v>1.1619999999999999</v>
+      </c>
+      <c r="H35" s="3">
+        <f t="shared" si="7"/>
+        <v>1.2244999999999999</v>
+      </c>
+      <c r="I35" s="2">
+        <f t="shared" si="9"/>
+        <v>2.1665000000000001</v>
+      </c>
+      <c r="J35" s="6">
+        <v>0</v>
+      </c>
+      <c r="K35" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="L35" s="6">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="M35" s="6">
+        <v>1.7765</v>
+      </c>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <v>33</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="3">
+        <f t="shared" si="4"/>
+        <v>3.17</v>
+      </c>
+      <c r="F36" s="3">
+        <f t="shared" si="5"/>
+        <v>3.2324999999999999</v>
+      </c>
+      <c r="G36" s="3">
+        <f t="shared" si="6"/>
+        <v>1.5499999999999998</v>
+      </c>
+      <c r="H36" s="3">
+        <f t="shared" si="7"/>
+        <v>1.6124999999999998</v>
+      </c>
+      <c r="I36" s="2">
+        <f t="shared" si="9"/>
+        <v>1.835</v>
+      </c>
+      <c r="J36" s="6">
+        <v>0</v>
+      </c>
+      <c r="K36" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="L36" s="6">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="M36" s="6">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="J1:M1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/实体 entity/实体骑乘高度.xlsx
+++ b/实体 entity/实体骑乘高度.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\tree-hole\实体 entity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A6803B8-BB34-4C37-BAC4-6FB967E29D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A28F616-4B24-4E0E-B975-A882788115F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="1.20.4+测试数据" sheetId="1" r:id="rId1"/>
-    <sheet name="1.20.4+组合数据" sheetId="2" r:id="rId2"/>
-    <sheet name="1.20.1-测试数据" sheetId="3" r:id="rId3"/>
-    <sheet name="1.20.1-组合数据" sheetId="4" r:id="rId4"/>
+    <sheet name="1.20.4+组合数据" sheetId="2" r:id="rId1"/>
+    <sheet name="1.20.1-组合数据" sheetId="4" r:id="rId2"/>
+    <sheet name="1.20.4+测试数据" sheetId="1" r:id="rId3"/>
+    <sheet name="1.20.1-测试数据" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="42">
   <si>
     <t>玩家</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -204,6 +204,10 @@
     <t>有轨高度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>快乐恶魂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -343,7 +347,247 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="30">
+  <dxfs count="54">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -822,64 +1066,64 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{ECBC2B67-FC40-458D-A11A-81B8166D56F6}" name="表7" displayName="表7" ref="A2:M36" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
-  <autoFilter ref="A2:M36" xr:uid="{ECBC2B67-FC40-458D-A11A-81B8166D56F6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{ECBC2B67-FC40-458D-A11A-81B8166D56F6}" name="表7" displayName="表7" ref="A2:M37" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
+  <autoFilter ref="A2:M37" xr:uid="{ECBC2B67-FC40-458D-A11A-81B8166D56F6}"/>
   <tableColumns count="13">
-    <tableColumn id="2" xr3:uid="{1A5B9393-745A-40B5-99A3-4C560CC7B2F3}" name="组合编号" dataDxfId="27"/>
-    <tableColumn id="15" xr3:uid="{3B8A2C49-42F1-4867-BF42-2822CDF5E16D}" name="矿车(A)" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{48622B21-7452-4541-82EE-988C88AE65A7}" name="船/竹筏(B)" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{3ABEA036-6A6C-45C5-AA84-DA2D9F697B3D}" name="生物(C)" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{33D96CCA-ACD8-46A8-A267-E02365DAC666}" name="无轨视高" dataDxfId="23">
+    <tableColumn id="2" xr3:uid="{1A5B9393-745A-40B5-99A3-4C560CC7B2F3}" name="组合编号" dataDxfId="51"/>
+    <tableColumn id="15" xr3:uid="{3B8A2C49-42F1-4867-BF42-2822CDF5E16D}" name="矿车(A)" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{48622B21-7452-4541-82EE-988C88AE65A7}" name="船/竹筏(B)" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{3ABEA036-6A6C-45C5-AA84-DA2D9F697B3D}" name="生物(C)" dataDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{33D96CCA-ACD8-46A8-A267-E02365DAC666}" name="无轨视高" dataDxfId="47">
       <calculatedColumnFormula>SUM(J3:L3)+1.62</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{598FE69C-AF3A-46F1-AA80-7BF4B0C020CC}" name="有轨视高" dataDxfId="22">
+    <tableColumn id="9" xr3:uid="{598FE69C-AF3A-46F1-AA80-7BF4B0C020CC}" name="有轨视高" dataDxfId="46">
       <calculatedColumnFormula>SUM(J3:L3)+0.0625+1.62</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F66481C1-D9A2-4C5D-B8A5-F66D7C951622}" name="无轨高度" dataDxfId="21">
+    <tableColumn id="6" xr3:uid="{F66481C1-D9A2-4C5D-B8A5-F66D7C951622}" name="无轨高度" dataDxfId="45">
       <calculatedColumnFormula>SUM(J3:L3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{F4B5C6C8-A44A-4E9B-84C0-2F1A0C1E9F82}" name="有轨高度" dataDxfId="20">
+    <tableColumn id="7" xr3:uid="{F4B5C6C8-A44A-4E9B-84C0-2F1A0C1E9F82}" name="有轨高度" dataDxfId="44">
       <calculatedColumnFormula>SUM(J3:L3)+0.0625</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B429005B-3C2A-4B29-BC01-522C8E5715A5}" name="生物窒息高度" dataDxfId="19">
+    <tableColumn id="5" xr3:uid="{B429005B-3C2A-4B29-BC01-522C8E5715A5}" name="生物窒息高度" dataDxfId="43">
       <calculatedColumnFormula>SUM(J3:K3)+M3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{52A6878A-9E03-4079-BD2A-D65774A088C3}" name="矿车(A)2" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{53922683-A52C-4BB1-8910-A8475D84622A}" name="船/竹筏(B)2" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{A29EB1E0-DDBB-4484-A5E5-D5BB3182F6F2}" name="生物(C)2" dataDxfId="16"/>
-    <tableColumn id="13" xr3:uid="{4547FA66-A0F5-4A59-A7D1-7C2E362EC1FF}" name="生物视高" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{52A6878A-9E03-4079-BD2A-D65774A088C3}" name="矿车(A)2" dataDxfId="42"/>
+    <tableColumn id="11" xr3:uid="{53922683-A52C-4BB1-8910-A8475D84622A}" name="船/竹筏(B)2" dataDxfId="41"/>
+    <tableColumn id="12" xr3:uid="{A29EB1E0-DDBB-4484-A5E5-D5BB3182F6F2}" name="生物(C)2" dataDxfId="40"/>
+    <tableColumn id="13" xr3:uid="{4547FA66-A0F5-4A59-A7D1-7C2E362EC1FF}" name="生物视高" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{27945CDA-254B-4AA6-84AD-AE71E61FA140}" name="表7_2" displayName="表7_2" ref="A2:M36" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{27945CDA-254B-4AA6-84AD-AE71E61FA140}" name="表7_2" displayName="表7_2" ref="A2:M36" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
   <autoFilter ref="A2:M36" xr:uid="{27945CDA-254B-4AA6-84AD-AE71E61FA140}"/>
   <tableColumns count="13">
-    <tableColumn id="2" xr3:uid="{E3252128-2842-475D-836E-19597AAACB23}" name="组合编号" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{1A256CD6-F969-4F8A-BF08-782638A053C7}" name="矿车(A)" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{139D25BD-5769-4E1F-A9B3-54F4E782916C}" name="船/竹筏(B)" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{590934DE-6D63-4E32-A2BD-E6D9EEFB943B}" name="生物(C)" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{4205D7C0-92A8-4837-939F-E2DA06176A19}" name="无轨视高" dataDxfId="8">
+    <tableColumn id="2" xr3:uid="{E3252128-2842-475D-836E-19597AAACB23}" name="组合编号" dataDxfId="36"/>
+    <tableColumn id="15" xr3:uid="{1A256CD6-F969-4F8A-BF08-782638A053C7}" name="矿车(A)" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{139D25BD-5769-4E1F-A9B3-54F4E782916C}" name="船/竹筏(B)" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{590934DE-6D63-4E32-A2BD-E6D9EEFB943B}" name="生物(C)" dataDxfId="33"/>
+    <tableColumn id="8" xr3:uid="{4205D7C0-92A8-4837-939F-E2DA06176A19}" name="无轨视高" dataDxfId="32">
       <calculatedColumnFormula>SUM(J3:L3)+1.62</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{67B3BB23-165B-4512-8ECD-5E32DF8E967C}" name="有轨视高" dataDxfId="7">
+    <tableColumn id="9" xr3:uid="{67B3BB23-165B-4512-8ECD-5E32DF8E967C}" name="有轨视高" dataDxfId="31">
       <calculatedColumnFormula>SUM(J3:L3)+0.0625+1.62</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{C1854081-3CCD-47A4-8AC7-A6D4D09865AF}" name="无轨高度" dataDxfId="6">
+    <tableColumn id="6" xr3:uid="{C1854081-3CCD-47A4-8AC7-A6D4D09865AF}" name="无轨高度" dataDxfId="30">
       <calculatedColumnFormula>SUM(J3:L3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{C13933C2-8933-4303-A309-B7187722B680}" name="有轨高度" dataDxfId="5">
+    <tableColumn id="7" xr3:uid="{C13933C2-8933-4303-A309-B7187722B680}" name="有轨高度" dataDxfId="29">
       <calculatedColumnFormula>SUM(J3:L3)+0.0625</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{A1FEBA74-5381-4FEA-B4CA-A6B60B7AF7D5}" name="生物窒息高度" dataDxfId="4">
+    <tableColumn id="5" xr3:uid="{A1FEBA74-5381-4FEA-B4CA-A6B60B7AF7D5}" name="生物窒息高度" dataDxfId="28">
       <calculatedColumnFormula>SUM(J3:K3)+M3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1664F24A-A49A-43FD-84D6-EA805F9ED691}" name="矿车(A)2" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{2AEE38F2-0B0B-4C64-923E-656338A16C44}" name="船/竹筏(B)2" dataDxfId="2"/>
-    <tableColumn id="12" xr3:uid="{44162916-A597-48D8-ABD1-2FEC989945C2}" name="生物(C)2" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{09CE5323-8E54-4DBC-AA57-EEF2127DE728}" name="生物视高" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{1664F24A-A49A-43FD-84D6-EA805F9ED691}" name="矿车(A)2" dataDxfId="27"/>
+    <tableColumn id="11" xr3:uid="{2AEE38F2-0B0B-4C64-923E-656338A16C44}" name="船/竹筏(B)2" dataDxfId="26"/>
+    <tableColumn id="12" xr3:uid="{44162916-A597-48D8-ABD1-2FEC989945C2}" name="生物(C)2" dataDxfId="25"/>
+    <tableColumn id="13" xr3:uid="{09CE5323-8E54-4DBC-AA57-EEF2127DE728}" name="生物视高" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1147,314 +1391,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.58203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.9140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.58203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.58203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.9140625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1.62</v>
-      </c>
-      <c r="D3" s="2">
-        <f>C3*16</f>
-        <v>25.92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2">
-        <v>6.25E-2</v>
-      </c>
-      <c r="D4" s="2">
-        <f t="shared" ref="D4:D24" si="0">C4*16</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="2">
-        <v>-0.41249999999999998</v>
-      </c>
-      <c r="D6" s="2">
-        <f t="shared" si="0"/>
-        <v>-6.6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="2">
-        <v>-0.41249999999999998</v>
-      </c>
-      <c r="D7" s="2">
-        <f t="shared" si="0"/>
-        <v>-6.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="2">
-        <v>-0.1</v>
-      </c>
-      <c r="D8" s="2">
-        <f t="shared" si="0"/>
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0.26874999999999999</v>
-      </c>
-      <c r="D9" s="2">
-        <f t="shared" si="0"/>
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0.51249999999999996</v>
-      </c>
-      <c r="D10" s="2">
-        <f t="shared" si="0"/>
-        <v>8.1999999999999993</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0.61250000000000004</v>
-      </c>
-      <c r="D11" s="2">
-        <f t="shared" si="0"/>
-        <v>9.8000000000000007</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0.71875</v>
-      </c>
-      <c r="D12" s="2">
-        <f t="shared" si="0"/>
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0.77</v>
-      </c>
-      <c r="D13" s="2">
-        <f t="shared" si="0"/>
-        <v>12.32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="2">
-        <v>0.84375</v>
-      </c>
-      <c r="D14" s="2">
-        <f t="shared" si="0"/>
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D15" s="2">
-        <f t="shared" si="0"/>
-        <v>17.600000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2">
-        <v>1.4</v>
-      </c>
-      <c r="D16" s="2">
-        <f t="shared" si="0"/>
-        <v>22.4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="2">
-        <f>0.25-1/16</f>
-        <v>0.1875</v>
-      </c>
-      <c r="D18" s="2">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="D20" s="2">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="2">
-        <f>0.25-1/16</f>
-        <v>0.1875</v>
-      </c>
-      <c r="D22" s="2">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="2">
-        <f t="shared" ref="C23:C24" si="1">0.25-1/16</f>
-        <v>0.1875</v>
-      </c>
-      <c r="D23" s="2">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="2">
-        <f t="shared" si="1"/>
-        <v>0.1875</v>
-      </c>
-      <c r="D24" s="2">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C1B65AC-A9AA-48F8-B54F-CBEF804346E2}">
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.75" style="3" bestFit="1" customWidth="1"/>
@@ -1543,19 +1481,19 @@
       </c>
       <c r="B3" s="2"/>
       <c r="E3" s="3">
-        <f t="shared" ref="E3" si="0">SUM(J3:L3)+1.62</f>
+        <f>SUM(J3:L3)+1.62</f>
         <v>1.62</v>
       </c>
       <c r="F3" s="3">
-        <f t="shared" ref="F3" si="1">SUM(J3:L3)+0.0625+1.62</f>
+        <f>SUM(J3:L3)+0.0625+1.62</f>
         <v>1.6825000000000001</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" ref="G3" si="2">SUM(J3:L3)</f>
+        <f>SUM(J3:L3)</f>
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <f t="shared" ref="H3" si="3">SUM(J3:L3)+0.0625</f>
+        <f>SUM(J3:L3)+0.0625</f>
         <v>6.25E-2</v>
       </c>
       <c r="J3" s="6"/>
@@ -1572,19 +1510,19 @@
         <v>12</v>
       </c>
       <c r="E4" s="3">
-        <f t="shared" ref="E4:E36" si="4">SUM(J4:L4)+1.62</f>
+        <f>SUM(J4:L4)+1.62</f>
         <v>1.2075</v>
       </c>
       <c r="F4" s="3">
-        <f t="shared" ref="F4:F36" si="5">SUM(J4:L4)+0.0625+1.62</f>
+        <f>SUM(J4:L4)+0.0625+1.62</f>
         <v>1.27</v>
       </c>
       <c r="G4" s="3">
-        <f t="shared" ref="G4:G36" si="6">SUM(J4:L4)</f>
+        <f>SUM(J4:L4)</f>
         <v>-0.41249999999999998</v>
       </c>
       <c r="H4" s="3">
-        <f t="shared" ref="H4:H36" si="7">SUM(J4:L4)+0.0625</f>
+        <f>SUM(J4:L4)+0.0625</f>
         <v>-0.35</v>
       </c>
       <c r="J4" s="6">
@@ -1604,19 +1542,19 @@
         <v>18</v>
       </c>
       <c r="E5" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM(J5:L5)+1.62</f>
         <v>1.2075</v>
       </c>
       <c r="F5" s="3">
-        <f t="shared" si="5"/>
+        <f>SUM(J5:L5)+0.0625+1.62</f>
         <v>1.27</v>
       </c>
       <c r="G5" s="3">
-        <f t="shared" si="6"/>
+        <f>SUM(J5:L5)</f>
         <v>-0.41249999999999998</v>
       </c>
       <c r="H5" s="3">
-        <f t="shared" si="7"/>
+        <f>SUM(J5:L5)+0.0625</f>
         <v>-0.35</v>
       </c>
       <c r="J5" s="6"/>
@@ -1635,19 +1573,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM(J6:L6)+1.62</f>
         <v>1.52</v>
       </c>
       <c r="F6" s="3">
-        <f t="shared" si="5"/>
+        <f>SUM(J6:L6)+0.0625+1.62</f>
         <v>1.5825</v>
       </c>
       <c r="G6" s="3">
-        <f t="shared" si="6"/>
+        <f>SUM(J6:L6)</f>
         <v>-0.1</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" si="7"/>
+        <f>SUM(J6:L6)+0.0625</f>
         <v>-3.7500000000000006E-2</v>
       </c>
       <c r="J6" s="6"/>
@@ -1740,23 +1678,23 @@
         <v>2</v>
       </c>
       <c r="E9" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM(J9:L9)+1.62</f>
         <v>1.8887500000000002</v>
       </c>
       <c r="F9" s="3">
-        <f t="shared" si="5"/>
+        <f>SUM(J9:L9)+0.0625+1.62</f>
         <v>1.9512500000000002</v>
       </c>
       <c r="G9" s="3">
-        <f t="shared" si="6"/>
+        <f>SUM(J9:L9)</f>
         <v>0.26874999999999999</v>
       </c>
       <c r="H9" s="3">
-        <f t="shared" si="7"/>
+        <f>SUM(J9:L9)+0.0625</f>
         <v>0.33124999999999999</v>
       </c>
       <c r="I9" s="2">
-        <f t="shared" ref="I9:I16" si="8">SUM(J9:K9)+M9</f>
+        <f>SUM(J9:K9)+M9</f>
         <v>0.76500000000000001</v>
       </c>
       <c r="J9" s="6"/>
@@ -1778,23 +1716,23 @@
         <v>3</v>
       </c>
       <c r="E10" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM(J10:L10)+1.62</f>
         <v>2.1325000000000003</v>
       </c>
       <c r="F10" s="3">
-        <f t="shared" si="5"/>
+        <f>SUM(J10:L10)+0.0625+1.62</f>
         <v>2.1950000000000003</v>
       </c>
       <c r="G10" s="3">
-        <f t="shared" si="6"/>
+        <f>SUM(J10:L10)</f>
         <v>0.51249999999999996</v>
       </c>
       <c r="H10" s="3">
-        <f t="shared" si="7"/>
+        <f>SUM(J10:L10)+0.0625</f>
         <v>0.57499999999999996</v>
       </c>
       <c r="I10" s="2">
-        <f t="shared" si="8"/>
+        <f>SUM(J10:K10)+M10</f>
         <v>1.425</v>
       </c>
       <c r="J10" s="6"/>
@@ -1816,23 +1754,23 @@
         <v>4</v>
       </c>
       <c r="E11" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM(J11:L11)+1.62</f>
         <v>2.2324999999999999</v>
       </c>
       <c r="F11" s="3">
-        <f t="shared" si="5"/>
+        <f>SUM(J11:L11)+0.0625+1.62</f>
         <v>2.2949999999999999</v>
       </c>
       <c r="G11" s="3">
-        <f t="shared" si="6"/>
+        <f>SUM(J11:L11)</f>
         <v>0.61250000000000004</v>
       </c>
       <c r="H11" s="3">
-        <f t="shared" si="7"/>
+        <f>SUM(J11:L11)+0.0625</f>
         <v>0.67500000000000004</v>
       </c>
       <c r="I11" s="2">
-        <f t="shared" si="8"/>
+        <f>SUM(J11:K11)+M11</f>
         <v>1.52</v>
       </c>
       <c r="J11" s="6"/>
@@ -1854,23 +1792,23 @@
         <v>5</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM(J12:L12)+1.62</f>
         <v>2.3387500000000001</v>
       </c>
       <c r="F12" s="3">
-        <f t="shared" si="5"/>
+        <f>SUM(J12:L12)+0.0625+1.62</f>
         <v>2.4012500000000001</v>
       </c>
       <c r="G12" s="3">
-        <f t="shared" si="6"/>
+        <f>SUM(J12:L12)</f>
         <v>0.71875</v>
       </c>
       <c r="H12" s="3">
-        <f t="shared" si="7"/>
+        <f>SUM(J12:L12)+0.0625</f>
         <v>0.78125</v>
       </c>
       <c r="I12" s="2">
-        <f t="shared" si="8"/>
+        <f>SUM(J12:K12)+M12</f>
         <v>1.52</v>
       </c>
       <c r="J12" s="6"/>
@@ -1892,23 +1830,23 @@
         <v>6</v>
       </c>
       <c r="E13" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM(J13:L13)+1.62</f>
         <v>2.39</v>
       </c>
       <c r="F13" s="3">
-        <f t="shared" si="5"/>
+        <f>SUM(J13:L13)+0.0625+1.62</f>
         <v>2.4525000000000001</v>
       </c>
       <c r="G13" s="3">
-        <f t="shared" si="6"/>
+        <f>SUM(J13:L13)</f>
         <v>0.77</v>
       </c>
       <c r="H13" s="3">
-        <f t="shared" si="7"/>
+        <f>SUM(J13:L13)+0.0625</f>
         <v>0.83250000000000002</v>
       </c>
       <c r="I13" s="2">
-        <f t="shared" si="8"/>
+        <f>SUM(J13:K13)+M13</f>
         <v>1.7765</v>
       </c>
       <c r="J13" s="6"/>
@@ -1930,23 +1868,23 @@
         <v>7</v>
       </c>
       <c r="E14" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM(J14:L14)+1.62</f>
         <v>2.4637500000000001</v>
       </c>
       <c r="F14" s="3">
-        <f t="shared" si="5"/>
+        <f>SUM(J14:L14)+0.0625+1.62</f>
         <v>2.5262500000000001</v>
       </c>
       <c r="G14" s="3">
-        <f t="shared" si="6"/>
+        <f>SUM(J14:L14)</f>
         <v>0.84375</v>
       </c>
       <c r="H14" s="3">
-        <f t="shared" si="7"/>
+        <f>SUM(J14:L14)+0.0625</f>
         <v>0.90625</v>
       </c>
       <c r="I14" s="2">
-        <f t="shared" si="8"/>
+        <f>SUM(J14:K14)+M14</f>
         <v>1.52</v>
       </c>
       <c r="J14" s="6"/>
@@ -1968,23 +1906,23 @@
         <v>16</v>
       </c>
       <c r="E15" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM(J15:L15)+1.62</f>
         <v>2.72</v>
       </c>
       <c r="F15" s="3">
-        <f t="shared" si="5"/>
+        <f>SUM(J15:L15)+0.0625+1.62</f>
         <v>2.7825000000000002</v>
       </c>
       <c r="G15" s="3">
-        <f t="shared" si="6"/>
+        <f>SUM(J15:L15)</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="H15" s="3">
-        <f t="shared" si="7"/>
+        <f>SUM(J15:L15)+0.0625</f>
         <v>1.1625000000000001</v>
       </c>
       <c r="I15" s="2">
-        <f t="shared" si="8"/>
+        <f>SUM(J15:K15)+M15</f>
         <v>1.4450000000000001</v>
       </c>
       <c r="J15" s="6"/>
@@ -2006,23 +1944,23 @@
         <v>8</v>
       </c>
       <c r="E16" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM(J16:L16)+1.62</f>
         <v>3.02</v>
       </c>
       <c r="F16" s="3">
-        <f t="shared" si="5"/>
+        <f>SUM(J16:L16)+0.0625+1.62</f>
         <v>3.0825</v>
       </c>
       <c r="G16" s="3">
-        <f t="shared" si="6"/>
+        <f>SUM(J16:L16)</f>
         <v>1.4</v>
       </c>
       <c r="H16" s="3">
-        <f t="shared" si="7"/>
+        <f>SUM(J16:L16)+0.0625</f>
         <v>1.4624999999999999</v>
       </c>
       <c r="I16" s="2">
-        <f t="shared" si="8"/>
+        <f>SUM(J16:K16)+M16</f>
         <v>2.2749999999999999</v>
       </c>
       <c r="J16" s="6"/>
@@ -2047,23 +1985,23 @@
         <v>2</v>
       </c>
       <c r="E17" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM(J17:L17)+1.62</f>
         <v>2.0762499999999999</v>
       </c>
       <c r="F17" s="3">
-        <f t="shared" si="5"/>
+        <f>SUM(J17:L17)+0.0625+1.62</f>
         <v>2.1387499999999999</v>
       </c>
       <c r="G17" s="3">
-        <f t="shared" si="6"/>
+        <f>SUM(J17:L17)</f>
         <v>0.45624999999999999</v>
       </c>
       <c r="H17" s="3">
-        <f t="shared" si="7"/>
+        <f>SUM(J17:L17)+0.0625</f>
         <v>0.51875000000000004</v>
       </c>
       <c r="I17" s="2">
-        <f t="shared" ref="I17:I36" si="9">SUM(J17:K17)+M17</f>
+        <f>SUM(J17:K17)+M17</f>
         <v>0.95250000000000001</v>
       </c>
       <c r="J17" s="6">
@@ -2090,23 +2028,23 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM(J18:L18)+1.62</f>
         <v>2.3200000000000003</v>
       </c>
       <c r="F18" s="3">
-        <f t="shared" si="5"/>
+        <f>SUM(J18:L18)+0.0625+1.62</f>
         <v>2.3825000000000003</v>
       </c>
       <c r="G18" s="3">
-        <f t="shared" si="6"/>
+        <f>SUM(J18:L18)</f>
         <v>0.7</v>
       </c>
       <c r="H18" s="3">
-        <f t="shared" si="7"/>
+        <f>SUM(J18:L18)+0.0625</f>
         <v>0.76249999999999996</v>
       </c>
       <c r="I18" s="2">
-        <f t="shared" si="9"/>
+        <f>SUM(J18:K18)+M18</f>
         <v>1.6125</v>
       </c>
       <c r="J18" s="6">
@@ -2133,23 +2071,23 @@
         <v>4</v>
       </c>
       <c r="E19" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM(J19:L19)+1.62</f>
         <v>2.42</v>
       </c>
       <c r="F19" s="3">
-        <f t="shared" si="5"/>
+        <f>SUM(J19:L19)+0.0625+1.62</f>
         <v>2.4824999999999999</v>
       </c>
       <c r="G19" s="3">
-        <f t="shared" si="6"/>
+        <f>SUM(J19:L19)</f>
         <v>0.8</v>
       </c>
       <c r="H19" s="3">
-        <f t="shared" si="7"/>
+        <f>SUM(J19:L19)+0.0625</f>
         <v>0.86250000000000004</v>
       </c>
       <c r="I19" s="2">
-        <f t="shared" si="9"/>
+        <f>SUM(J19:K19)+M19</f>
         <v>1.7075</v>
       </c>
       <c r="J19" s="6">
@@ -2176,23 +2114,23 @@
         <v>5</v>
       </c>
       <c r="E20" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM(J20:L20)+1.62</f>
         <v>1.3387500000000001</v>
       </c>
       <c r="F20" s="3">
-        <f t="shared" si="5"/>
+        <f>SUM(J20:L20)+0.0625+1.62</f>
         <v>1.4012500000000001</v>
       </c>
       <c r="G20" s="3">
-        <f t="shared" si="6"/>
+        <f>SUM(J20:L20)</f>
         <v>-0.28125</v>
       </c>
       <c r="H20" s="3">
-        <f t="shared" si="7"/>
+        <f>SUM(J20:L20)+0.0625</f>
         <v>-0.21875</v>
       </c>
       <c r="I20" s="2">
-        <f t="shared" si="9"/>
+        <f>SUM(J20:K20)+M20</f>
         <v>0.52</v>
       </c>
       <c r="J20" s="6">
@@ -2219,23 +2157,23 @@
         <v>6</v>
       </c>
       <c r="E21" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM(J21:L21)+1.62</f>
         <v>1.3900000000000001</v>
       </c>
       <c r="F21" s="3">
-        <f t="shared" si="5"/>
+        <f>SUM(J21:L21)+0.0625+1.62</f>
         <v>1.4525000000000001</v>
       </c>
       <c r="G21" s="3">
-        <f t="shared" si="6"/>
+        <f>SUM(J21:L21)</f>
         <v>-0.22999999999999998</v>
       </c>
       <c r="H21" s="3">
-        <f t="shared" si="7"/>
+        <f>SUM(J21:L21)+0.0625</f>
         <v>-0.16749999999999998</v>
       </c>
       <c r="I21" s="2">
-        <f t="shared" si="9"/>
+        <f>SUM(J21:K21)+M21</f>
         <v>0.77649999999999997</v>
       </c>
       <c r="J21" s="6">
@@ -2262,23 +2200,23 @@
         <v>7</v>
       </c>
       <c r="E22" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM(J22:L22)+1.62</f>
         <v>2.6512500000000001</v>
       </c>
       <c r="F22" s="3">
-        <f t="shared" si="5"/>
+        <f>SUM(J22:L22)+0.0625+1.62</f>
         <v>2.7137500000000001</v>
       </c>
       <c r="G22" s="3">
-        <f t="shared" si="6"/>
+        <f>SUM(J22:L22)</f>
         <v>1.03125</v>
       </c>
       <c r="H22" s="3">
-        <f t="shared" si="7"/>
+        <f>SUM(J22:L22)+0.0625</f>
         <v>1.09375</v>
       </c>
       <c r="I22" s="2">
-        <f t="shared" si="9"/>
+        <f>SUM(J22:K22)+M22</f>
         <v>1.7075</v>
       </c>
       <c r="J22" s="6">
@@ -2305,23 +2243,23 @@
         <v>16</v>
       </c>
       <c r="E23" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM(J23:L23)+1.62</f>
         <v>2.97</v>
       </c>
       <c r="F23" s="3">
-        <f t="shared" si="5"/>
+        <f>SUM(J23:L23)+0.0625+1.62</f>
         <v>3.0325000000000002</v>
       </c>
       <c r="G23" s="3">
-        <f t="shared" si="6"/>
+        <f>SUM(J23:L23)</f>
         <v>1.35</v>
       </c>
       <c r="H23" s="3">
-        <f t="shared" si="7"/>
+        <f>SUM(J23:L23)+0.0625</f>
         <v>1.4125000000000001</v>
       </c>
       <c r="I23" s="2">
-        <f t="shared" si="9"/>
+        <f>SUM(J23:K23)+M23</f>
         <v>1.6950000000000001</v>
       </c>
       <c r="J23" s="6">
@@ -2348,23 +2286,23 @@
         <v>8</v>
       </c>
       <c r="E24" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM(J24:L24)+1.62</f>
         <v>3.2075</v>
       </c>
       <c r="F24" s="3">
-        <f t="shared" si="5"/>
+        <f>SUM(J24:L24)+0.0625+1.62</f>
         <v>3.27</v>
       </c>
       <c r="G24" s="3">
-        <f t="shared" si="6"/>
+        <f>SUM(J24:L24)</f>
         <v>1.5874999999999999</v>
       </c>
       <c r="H24" s="3">
-        <f t="shared" si="7"/>
+        <f>SUM(J24:L24)+0.0625</f>
         <v>1.65</v>
       </c>
       <c r="I24" s="2">
-        <f t="shared" si="9"/>
+        <f>SUM(J24:K24)+M24</f>
         <v>2.4624999999999999</v>
       </c>
       <c r="J24" s="6">
@@ -2381,314 +2319,308 @@
       <c r="O24" s="3"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
-        <v>22</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="E25" s="3">
-        <f t="shared" si="4"/>
-        <v>2.0762499999999999</v>
+        <f>SUM(J25:L25)+1.62</f>
+        <v>5.7075000000000005</v>
       </c>
       <c r="F25" s="3">
-        <f t="shared" si="5"/>
-        <v>2.1387499999999999</v>
+        <f>SUM(J25:L25)+0.0625+1.62</f>
+        <v>5.7700000000000005</v>
       </c>
       <c r="G25" s="3">
-        <f t="shared" si="6"/>
-        <v>0.45624999999999999</v>
+        <f>SUM(J25:L25)</f>
+        <v>4.0875000000000004</v>
       </c>
       <c r="H25" s="3">
-        <f t="shared" si="7"/>
-        <v>0.51875000000000004</v>
+        <f>SUM(J25:L25)+0.0625</f>
+        <v>4.1500000000000004</v>
       </c>
       <c r="I25" s="2">
-        <f t="shared" si="9"/>
-        <v>0.95250000000000001</v>
-      </c>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6">
-        <v>0.1875</v>
-      </c>
+        <f>SUM(J25:K25)+M25</f>
+        <v>3.2875000000000001</v>
+      </c>
+      <c r="J25" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="K25" s="6"/>
       <c r="L25" s="6">
-        <v>0.26874999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="M25" s="6">
-        <v>0.76500000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E26" s="3">
-        <f t="shared" si="4"/>
-        <v>2.5775000000000001</v>
+        <f>SUM(J26:L26)+1.62</f>
+        <v>2.0762499999999999</v>
       </c>
       <c r="F26" s="3">
-        <f t="shared" si="5"/>
-        <v>2.64</v>
+        <f>SUM(J26:L26)+0.0625+1.62</f>
+        <v>2.1387499999999999</v>
       </c>
       <c r="G26" s="3">
-        <f t="shared" si="6"/>
-        <v>0.95750000000000002</v>
+        <f>SUM(J26:L26)</f>
+        <v>0.45624999999999999</v>
       </c>
       <c r="H26" s="3">
-        <f t="shared" si="7"/>
-        <v>1.02</v>
+        <f>SUM(J26:L26)+0.0625</f>
+        <v>0.51875000000000004</v>
       </c>
       <c r="I26" s="2">
-        <f t="shared" si="9"/>
-        <v>1.964</v>
+        <f>SUM(J26:K26)+M26</f>
+        <v>0.95250000000000001</v>
       </c>
       <c r="J26" s="6"/>
       <c r="K26" s="6">
         <v>0.1875</v>
       </c>
       <c r="L26" s="6">
-        <v>0.77</v>
+        <v>0.26874999999999999</v>
       </c>
       <c r="M26" s="6">
-        <v>1.7765</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E27" s="3">
-        <f t="shared" si="4"/>
-        <v>2.9075000000000002</v>
+        <f>SUM(J27:L27)+1.62</f>
+        <v>2.5775000000000001</v>
       </c>
       <c r="F27" s="3">
-        <f t="shared" si="5"/>
-        <v>2.97</v>
+        <f>SUM(J27:L27)+0.0625+1.62</f>
+        <v>2.64</v>
       </c>
       <c r="G27" s="3">
-        <f t="shared" si="6"/>
-        <v>1.2875000000000001</v>
+        <f>SUM(J27:L27)</f>
+        <v>0.95750000000000002</v>
       </c>
       <c r="H27" s="3">
-        <f t="shared" si="7"/>
-        <v>1.35</v>
+        <f>SUM(J27:L27)+0.0625</f>
+        <v>1.02</v>
       </c>
       <c r="I27" s="2">
-        <f t="shared" si="9"/>
-        <v>1.6325000000000001</v>
+        <f>SUM(J27:K27)+M27</f>
+        <v>1.964</v>
       </c>
       <c r="J27" s="6"/>
       <c r="K27" s="6">
         <v>0.1875</v>
       </c>
       <c r="L27" s="6">
-        <v>1.1000000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="M27" s="6">
-        <v>1.4450000000000001</v>
+        <v>1.7765</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E28" s="3">
-        <f t="shared" si="4"/>
-        <v>2.3887499999999999</v>
+        <f>SUM(J28:L28)+1.62</f>
+        <v>2.9075000000000002</v>
       </c>
       <c r="F28" s="3">
-        <f t="shared" si="5"/>
-        <v>2.4512499999999999</v>
+        <f>SUM(J28:L28)+0.0625+1.62</f>
+        <v>2.97</v>
       </c>
       <c r="G28" s="3">
-        <f t="shared" si="6"/>
-        <v>0.76875000000000004</v>
+        <f>SUM(J28:L28)</f>
+        <v>1.2875000000000001</v>
       </c>
       <c r="H28" s="3">
-        <f t="shared" si="7"/>
-        <v>0.83125000000000004</v>
+        <f>SUM(J28:L28)+0.0625</f>
+        <v>1.35</v>
       </c>
       <c r="I28" s="2">
-        <f t="shared" si="9"/>
-        <v>1.2650000000000001</v>
+        <f>SUM(J28:K28)+M28</f>
+        <v>1.6325000000000001</v>
       </c>
       <c r="J28" s="6"/>
       <c r="K28" s="6">
-        <v>0.5</v>
+        <v>0.1875</v>
       </c>
       <c r="L28" s="6">
-        <v>0.26874999999999999</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="M28" s="6">
-        <v>0.76500000000000001</v>
+        <v>1.4450000000000001</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E29" s="3">
-        <f t="shared" si="4"/>
-        <v>2.89</v>
+        <f>SUM(J29:L29)+1.62</f>
+        <v>2.3887499999999999</v>
       </c>
       <c r="F29" s="3">
-        <f t="shared" si="5"/>
-        <v>2.9525000000000001</v>
+        <f>SUM(J29:L29)+0.0625+1.62</f>
+        <v>2.4512499999999999</v>
       </c>
       <c r="G29" s="3">
-        <f t="shared" si="6"/>
-        <v>1.27</v>
+        <f>SUM(J29:L29)</f>
+        <v>0.76875000000000004</v>
       </c>
       <c r="H29" s="3">
-        <f t="shared" si="7"/>
-        <v>1.3325</v>
+        <f>SUM(J29:L29)+0.0625</f>
+        <v>0.83125000000000004</v>
       </c>
       <c r="I29" s="2">
-        <f t="shared" si="9"/>
-        <v>2.2765</v>
+        <f>SUM(J29:K29)+M29</f>
+        <v>1.2650000000000001</v>
       </c>
       <c r="J29" s="6"/>
       <c r="K29" s="6">
         <v>0.5</v>
       </c>
       <c r="L29" s="6">
-        <v>0.77</v>
+        <v>0.26874999999999999</v>
       </c>
       <c r="M29" s="6">
-        <v>1.7765</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E30" s="3">
-        <f t="shared" si="4"/>
-        <v>3.22</v>
+        <f>SUM(J30:L30)+1.62</f>
+        <v>2.89</v>
       </c>
       <c r="F30" s="3">
-        <f t="shared" si="5"/>
-        <v>3.2825000000000002</v>
+        <f>SUM(J30:L30)+0.0625+1.62</f>
+        <v>2.9525000000000001</v>
       </c>
       <c r="G30" s="3">
-        <f t="shared" si="6"/>
-        <v>1.6</v>
+        <f>SUM(J30:L30)</f>
+        <v>1.27</v>
       </c>
       <c r="H30" s="3">
-        <f t="shared" si="7"/>
-        <v>1.6625000000000001</v>
+        <f>SUM(J30:L30)+0.0625</f>
+        <v>1.3325</v>
       </c>
       <c r="I30" s="2">
-        <f t="shared" si="9"/>
-        <v>1.9450000000000001</v>
+        <f>SUM(J30:K30)+M30</f>
+        <v>2.2765</v>
       </c>
       <c r="J30" s="6"/>
       <c r="K30" s="6">
         <v>0.5</v>
       </c>
       <c r="L30" s="6">
-        <v>1.1000000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="M30" s="6">
-        <v>1.4450000000000001</v>
+        <v>1.7765</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
-        <v>28</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E31" s="3">
-        <f t="shared" si="4"/>
-        <v>2.2637499999999999</v>
+        <f>SUM(J31:L31)+1.62</f>
+        <v>3.22</v>
       </c>
       <c r="F31" s="3">
-        <f t="shared" si="5"/>
-        <v>2.3262499999999999</v>
+        <f>SUM(J31:L31)+0.0625+1.62</f>
+        <v>3.2825000000000002</v>
       </c>
       <c r="G31" s="3">
-        <f t="shared" si="6"/>
-        <v>0.64375000000000004</v>
+        <f>SUM(J31:L31)</f>
+        <v>1.6</v>
       </c>
       <c r="H31" s="3">
-        <f t="shared" si="7"/>
-        <v>0.70625000000000004</v>
+        <f>SUM(J31:L31)+0.0625</f>
+        <v>1.6625000000000001</v>
       </c>
       <c r="I31" s="2">
-        <f t="shared" si="9"/>
-        <v>1.1400000000000001</v>
-      </c>
-      <c r="J31" s="6">
-        <v>0.1875</v>
-      </c>
+        <f>SUM(J31:K31)+M31</f>
+        <v>1.9450000000000001</v>
+      </c>
+      <c r="J31" s="6"/>
       <c r="K31" s="6">
-        <v>0.1875</v>
+        <v>0.5</v>
       </c>
       <c r="L31" s="6">
-        <v>0.26874999999999999</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="M31" s="6">
-        <v>0.76500000000000001</v>
+        <v>1.4450000000000001</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>19</v>
@@ -2697,27 +2629,27 @@
         <v>15</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E32" s="3">
-        <f t="shared" si="4"/>
-        <v>2.7650000000000001</v>
+        <f>SUM(J32:L32)+1.62</f>
+        <v>2.2637499999999999</v>
       </c>
       <c r="F32" s="3">
-        <f t="shared" si="5"/>
-        <v>2.8275000000000001</v>
+        <f>SUM(J32:L32)+0.0625+1.62</f>
+        <v>2.3262499999999999</v>
       </c>
       <c r="G32" s="3">
-        <f t="shared" si="6"/>
-        <v>1.145</v>
+        <f>SUM(J32:L32)</f>
+        <v>0.64375000000000004</v>
       </c>
       <c r="H32" s="3">
-        <f t="shared" si="7"/>
-        <v>1.2075</v>
+        <f>SUM(J32:L32)+0.0625</f>
+        <v>0.70625000000000004</v>
       </c>
       <c r="I32" s="2">
-        <f t="shared" si="9"/>
-        <v>2.1515</v>
+        <f>SUM(J32:K32)+M32</f>
+        <v>1.1400000000000001</v>
       </c>
       <c r="J32" s="6">
         <v>0.1875</v>
@@ -2726,17 +2658,17 @@
         <v>0.1875</v>
       </c>
       <c r="L32" s="6">
-        <v>0.77</v>
+        <v>0.26874999999999999</v>
       </c>
       <c r="M32" s="6">
-        <v>1.7765</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>19</v>
@@ -2745,27 +2677,27 @@
         <v>15</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E33" s="3">
-        <f t="shared" si="4"/>
-        <v>3.0950000000000002</v>
+        <f>SUM(J33:L33)+1.62</f>
+        <v>2.7650000000000001</v>
       </c>
       <c r="F33" s="3">
-        <f t="shared" si="5"/>
-        <v>3.1575000000000002</v>
+        <f>SUM(J33:L33)+0.0625+1.62</f>
+        <v>2.8275000000000001</v>
       </c>
       <c r="G33" s="3">
-        <f t="shared" si="6"/>
-        <v>1.4750000000000001</v>
+        <f>SUM(J33:L33)</f>
+        <v>1.145</v>
       </c>
       <c r="H33" s="3">
-        <f t="shared" si="7"/>
-        <v>1.5375000000000001</v>
+        <f>SUM(J33:L33)+0.0625</f>
+        <v>1.2075</v>
       </c>
       <c r="I33" s="2">
-        <f t="shared" si="9"/>
-        <v>1.82</v>
+        <f>SUM(J33:K33)+M33</f>
+        <v>2.1515</v>
       </c>
       <c r="J33" s="6">
         <v>0.1875</v>
@@ -2774,65 +2706,65 @@
         <v>0.1875</v>
       </c>
       <c r="L33" s="6">
-        <v>1.1000000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="M33" s="6">
-        <v>1.4450000000000001</v>
+        <v>1.7765</v>
       </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E34" s="3">
-        <f t="shared" si="4"/>
-        <v>2.5762499999999999</v>
+        <f>SUM(J34:L34)+1.62</f>
+        <v>3.0950000000000002</v>
       </c>
       <c r="F34" s="3">
-        <f t="shared" si="5"/>
-        <v>2.6387499999999999</v>
+        <f>SUM(J34:L34)+0.0625+1.62</f>
+        <v>3.1575000000000002</v>
       </c>
       <c r="G34" s="3">
-        <f t="shared" si="6"/>
-        <v>0.95625000000000004</v>
+        <f>SUM(J34:L34)</f>
+        <v>1.4750000000000001</v>
       </c>
       <c r="H34" s="3">
-        <f t="shared" si="7"/>
-        <v>1.01875</v>
+        <f>SUM(J34:L34)+0.0625</f>
+        <v>1.5375000000000001</v>
       </c>
       <c r="I34" s="2">
-        <f t="shared" si="9"/>
-        <v>1.4525000000000001</v>
+        <f>SUM(J34:K34)+M34</f>
+        <v>1.82</v>
       </c>
       <c r="J34" s="6">
         <v>0.1875</v>
       </c>
       <c r="K34" s="6">
-        <v>0.5</v>
+        <v>0.1875</v>
       </c>
       <c r="L34" s="6">
-        <v>0.26874999999999999</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="M34" s="6">
-        <v>0.76500000000000001</v>
+        <v>1.4450000000000001</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>19</v>
@@ -2841,27 +2773,27 @@
         <v>1</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E35" s="3">
-        <f t="shared" si="4"/>
-        <v>3.0775000000000001</v>
+        <f>SUM(J35:L35)+1.62</f>
+        <v>2.5762499999999999</v>
       </c>
       <c r="F35" s="3">
-        <f t="shared" si="5"/>
-        <v>3.14</v>
+        <f>SUM(J35:L35)+0.0625+1.62</f>
+        <v>2.6387499999999999</v>
       </c>
       <c r="G35" s="3">
-        <f t="shared" si="6"/>
-        <v>1.4575</v>
+        <f>SUM(J35:L35)</f>
+        <v>0.95625000000000004</v>
       </c>
       <c r="H35" s="3">
-        <f t="shared" si="7"/>
-        <v>1.52</v>
+        <f>SUM(J35:L35)+0.0625</f>
+        <v>1.01875</v>
       </c>
       <c r="I35" s="2">
-        <f t="shared" si="9"/>
-        <v>2.464</v>
+        <f>SUM(J35:K35)+M35</f>
+        <v>1.4525000000000001</v>
       </c>
       <c r="J35" s="6">
         <v>0.1875</v>
@@ -2870,17 +2802,17 @@
         <v>0.5</v>
       </c>
       <c r="L35" s="6">
-        <v>0.77</v>
+        <v>0.26874999999999999</v>
       </c>
       <c r="M35" s="6">
-        <v>1.7765</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>19</v>
@@ -2889,27 +2821,27 @@
         <v>1</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E36" s="3">
-        <f t="shared" si="4"/>
-        <v>3.4075000000000002</v>
+        <f>SUM(J36:L36)+1.62</f>
+        <v>3.0775000000000001</v>
       </c>
       <c r="F36" s="3">
-        <f t="shared" si="5"/>
-        <v>3.47</v>
+        <f>SUM(J36:L36)+0.0625+1.62</f>
+        <v>3.14</v>
       </c>
       <c r="G36" s="3">
-        <f t="shared" si="6"/>
-        <v>1.7875000000000001</v>
+        <f>SUM(J36:L36)</f>
+        <v>1.4575</v>
       </c>
       <c r="H36" s="3">
-        <f t="shared" si="7"/>
-        <v>1.85</v>
+        <f>SUM(J36:L36)+0.0625</f>
+        <v>1.52</v>
       </c>
       <c r="I36" s="2">
-        <f t="shared" si="9"/>
-        <v>2.1325000000000003</v>
+        <f>SUM(J36:K36)+M36</f>
+        <v>2.464</v>
       </c>
       <c r="J36" s="6">
         <v>0.1875</v>
@@ -2918,13 +2850,61 @@
         <v>0.5</v>
       </c>
       <c r="L36" s="6">
-        <v>1.1000000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="M36" s="6">
-        <v>1.4450000000000001</v>
+        <v>1.7765</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <v>33</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="3">
+        <f>SUM(J37:L37)+1.62</f>
+        <v>3.4075000000000002</v>
+      </c>
+      <c r="F37" s="3">
+        <f>SUM(J37:L37)+0.0625+1.62</f>
+        <v>3.47</v>
+      </c>
+      <c r="G37" s="3">
+        <f>SUM(J37:L37)</f>
+        <v>1.7875000000000001</v>
+      </c>
+      <c r="H37" s="3">
+        <f>SUM(J37:L37)+0.0625</f>
+        <v>1.85</v>
+      </c>
+      <c r="I37" s="2">
+        <f>SUM(J37:K37)+M37</f>
+        <v>2.1325000000000003</v>
+      </c>
+      <c r="J37" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="K37" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="L37" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M37" s="6">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2933,346 +2913,27 @@
     <mergeCell ref="E1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="E3:I37">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="between">
+      <formula>1</formula>
+      <formula>2</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThanOrEqual">
+      <formula>2</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEB9D88C-9594-4ED7-93DA-80DA60D28A9A}">
-  <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1.62</v>
-      </c>
-      <c r="D3" s="2">
-        <f>C3*16</f>
-        <v>25.92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2">
-        <v>6.25E-2</v>
-      </c>
-      <c r="D4" s="2">
-        <f t="shared" ref="D4:D24" si="0">C4*16</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="2">
-        <v>-0.35</v>
-      </c>
-      <c r="D6" s="2">
-        <f t="shared" si="0"/>
-        <v>-5.6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="2">
-        <v>-0.35</v>
-      </c>
-      <c r="D7" s="2">
-        <f t="shared" si="0"/>
-        <v>-5.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="2">
-        <v>-0.1</v>
-      </c>
-      <c r="D8" s="2">
-        <f t="shared" si="0"/>
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="D9" s="2">
-        <f t="shared" si="0"/>
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="D10" s="2">
-        <f t="shared" si="0"/>
-        <v>8.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="D11" s="2">
-        <f t="shared" si="0"/>
-        <v>9.6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0.66249999999999998</v>
-      </c>
-      <c r="D12" s="2">
-        <f t="shared" si="0"/>
-        <v>10.6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0.77200000000000002</v>
-      </c>
-      <c r="D13" s="2">
-        <f t="shared" si="0"/>
-        <v>12.352</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="2">
-        <v>0.85</v>
-      </c>
-      <c r="D14" s="2">
-        <f t="shared" si="0"/>
-        <v>13.6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="D15" s="2">
-        <f t="shared" si="0"/>
-        <v>18.559999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2">
-        <v>1.425</v>
-      </c>
-      <c r="D16" s="2">
-        <f t="shared" si="0"/>
-        <v>22.8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="2">
-        <v>0.04</v>
-      </c>
-      <c r="D18" s="2">
-        <f t="shared" si="0"/>
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="2">
-        <v>0.39</v>
-      </c>
-      <c r="D20" s="2">
-        <f t="shared" si="0"/>
-        <v>6.24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D22" s="2">
-        <f t="shared" si="0"/>
-        <v>2.2400000000000002</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D23" s="2">
-        <f t="shared" si="0"/>
-        <v>2.2400000000000002</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D24" s="2">
-        <f t="shared" si="0"/>
-        <v>2.2400000000000002</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3807DD25-8EFF-4D65-BFF6-A690D0D26684}">
   <dimension ref="A1:O36"/>
   <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -3363,19 +3024,19 @@
       </c>
       <c r="B3" s="2"/>
       <c r="E3" s="3">
-        <f t="shared" ref="E3:E36" si="0">SUM(J3:L3)+1.62</f>
+        <f t="shared" ref="E3" si="0">SUM(J3:L3)+1.62</f>
         <v>1.62</v>
       </c>
       <c r="F3" s="3">
-        <f t="shared" ref="F3:F36" si="1">SUM(J3:L3)+0.0625+1.62</f>
+        <f t="shared" ref="F3" si="1">SUM(J3:L3)+0.0625+1.62</f>
         <v>1.6825000000000001</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" ref="G3:G30" si="2">SUM(J3:L3)</f>
+        <f t="shared" ref="G3" si="2">SUM(J3:L3)</f>
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <f t="shared" ref="H3:H36" si="3">SUM(J3:L3)+0.0625</f>
+        <f t="shared" ref="H3" si="3">SUM(J3:L3)+0.0625</f>
         <v>6.25E-2</v>
       </c>
       <c r="J3" s="6"/>
@@ -4753,9 +4414,688 @@
     <mergeCell ref="J1:M1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="E3:I36">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
+      <formula>2</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+      <formula>1</formula>
+      <formula>2</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.58203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.9140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.58203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.58203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.9140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1.62</v>
+      </c>
+      <c r="D3" s="2">
+        <f>C3*16</f>
+        <v>25.92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2">
+        <v>6.25E-2</v>
+      </c>
+      <c r="D4" s="2">
+        <f t="shared" ref="D4:D25" si="0">C4*16</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>-0.41249999999999998</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="0"/>
+        <v>-6.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>-0.41249999999999998</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="0"/>
+        <v>-6.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="0"/>
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.26874999999999999</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="0"/>
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="0"/>
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.61250000000000004</v>
+      </c>
+      <c r="D11" s="2">
+        <f t="shared" si="0"/>
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.71875</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.77</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" si="0"/>
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.84375</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" si="0"/>
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="0"/>
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="D17" s="2">
+        <f t="shared" si="0"/>
+        <v>54.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="2">
+        <f>0.25-1/16</f>
+        <v>0.1875</v>
+      </c>
+      <c r="D19" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D21" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="2">
+        <f>0.25-1/16</f>
+        <v>0.1875</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="2">
+        <f t="shared" ref="C24:C25" si="1">0.25-1/16</f>
+        <v>0.1875</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="2">
+        <f t="shared" si="1"/>
+        <v>0.1875</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="D26" s="2">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEB9D88C-9594-4ED7-93DA-80DA60D28A9A}">
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1.62</v>
+      </c>
+      <c r="D3" s="2">
+        <f>C3*16</f>
+        <v>25.92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2">
+        <v>6.25E-2</v>
+      </c>
+      <c r="D4" s="2">
+        <f t="shared" ref="D4:D24" si="0">C4*16</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>-0.35</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="0"/>
+        <v>-5.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>-0.35</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="0"/>
+        <v>-5.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="0"/>
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="0"/>
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="0"/>
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="D11" s="2">
+        <f t="shared" si="0"/>
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.66249999999999998</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" si="0"/>
+        <v>12.352</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="0"/>
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" si="0"/>
+        <v>18.559999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1.425</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="0"/>
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="D18" s="2">
+        <f t="shared" si="0"/>
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="D20" s="2">
+        <f t="shared" si="0"/>
+        <v>6.24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D22" s="2">
+        <f t="shared" si="0"/>
+        <v>2.2400000000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="0"/>
+        <v>2.2400000000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="0"/>
+        <v>2.2400000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/实体 entity/实体骑乘高度.xlsx
+++ b/实体 entity/实体骑乘高度.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\tree-hole\实体 entity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A28F616-4B24-4E0E-B975-A882788115F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7035D3C7-3814-49FF-A628-CA7627D2FD1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="1.20.4+组合数据" sheetId="2" r:id="rId1"/>
-    <sheet name="1.20.1-组合数据" sheetId="4" r:id="rId2"/>
-    <sheet name="1.20.4+测试数据" sheetId="1" r:id="rId3"/>
-    <sheet name="1.20.1-测试数据" sheetId="3" r:id="rId4"/>
+    <sheet name="1.20.4+组合数据(像素)" sheetId="5" r:id="rId1"/>
+    <sheet name="1.20.4+组合数据(米)" sheetId="2" r:id="rId2"/>
+    <sheet name="1.20.1-组合数据(像素)" sheetId="6" r:id="rId3"/>
+    <sheet name="1.20.1-组合数据(米)" sheetId="4" r:id="rId4"/>
+    <sheet name="1.20.4+测试数据" sheetId="1" r:id="rId5"/>
+    <sheet name="1.20.1-测试数据" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="42">
   <si>
     <t>玩家</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -302,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -340,14 +342,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="54">
+  <dxfs count="66">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -395,186 +403,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -921,6 +749,242 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFBFBFBF"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1052,6 +1116,242 @@
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFBFBFBF"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1066,64 +1366,128 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{ECBC2B67-FC40-458D-A11A-81B8166D56F6}" name="表7" displayName="表7" ref="A2:M37" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{084B3CEE-A088-4105-AE88-1BFE8C0F457C}" name="表7_3" displayName="表7_3" ref="A2:M37" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
   <autoFilter ref="A2:M37" xr:uid="{ECBC2B67-FC40-458D-A11A-81B8166D56F6}"/>
   <tableColumns count="13">
-    <tableColumn id="2" xr3:uid="{1A5B9393-745A-40B5-99A3-4C560CC7B2F3}" name="组合编号" dataDxfId="51"/>
-    <tableColumn id="15" xr3:uid="{3B8A2C49-42F1-4867-BF42-2822CDF5E16D}" name="矿车(A)" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{48622B21-7452-4541-82EE-988C88AE65A7}" name="船/竹筏(B)" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{3ABEA036-6A6C-45C5-AA84-DA2D9F697B3D}" name="生物(C)" dataDxfId="48"/>
-    <tableColumn id="8" xr3:uid="{33D96CCA-ACD8-46A8-A267-E02365DAC666}" name="无轨视高" dataDxfId="47">
-      <calculatedColumnFormula>SUM(J3:L3)+1.62</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{28FA0ADE-FA24-4C69-8AC0-B8136613F3B9}" name="组合编号" dataDxfId="63"/>
+    <tableColumn id="15" xr3:uid="{39F2DF11-91FD-4588-80CC-35CC7D44B70F}" name="矿车(A)" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{0F07B471-4667-4108-969E-BA2015CF52FF}" name="船/竹筏(B)" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{97BF810A-53C7-451D-9919-6761B4340729}" name="生物(C)" dataDxfId="60"/>
+    <tableColumn id="8" xr3:uid="{E65C589F-3C0F-42D2-B8A0-926C9E722354}" name="无轨视高" dataDxfId="59">
+      <calculatedColumnFormula>INT(SUM(J3:L3)+1.62)&amp;"m "&amp;((SUM(J3:L3)+1.62)-INT(SUM(J3:L3)+1.62))*16&amp;"px"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{598FE69C-AF3A-46F1-AA80-7BF4B0C020CC}" name="有轨视高" dataDxfId="46">
-      <calculatedColumnFormula>SUM(J3:L3)+0.0625+1.62</calculatedColumnFormula>
+    <tableColumn id="9" xr3:uid="{A6ABFFDB-354E-4C09-9E8E-EA8D1A01E7AE}" name="有轨视高" dataDxfId="58">
+      <calculatedColumnFormula>INT(SUM(J3:L3)+0.0625+1.62)&amp;"m "&amp;((SUM(J3:L3)+0.0625+1.62)-INT(SUM(J3:L3)+0.0625+1.62))*16&amp;"px"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F66481C1-D9A2-4C5D-B8A5-F66D7C951622}" name="无轨高度" dataDxfId="45">
-      <calculatedColumnFormula>SUM(J3:L3)</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{3BB918C4-E0AA-43D5-9296-02D16A459FCB}" name="无轨高度" dataDxfId="57">
+      <calculatedColumnFormula>INT(SUM(J3:L3))&amp;"m "&amp;((SUM(J3:L3))-INT(SUM(J3:L3)))*16&amp;"px"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{F4B5C6C8-A44A-4E9B-84C0-2F1A0C1E9F82}" name="有轨高度" dataDxfId="44">
-      <calculatedColumnFormula>SUM(J3:L3)+0.0625</calculatedColumnFormula>
+    <tableColumn id="7" xr3:uid="{FE577ECA-8793-41AD-891F-AF1FD4FC96C9}" name="有轨高度" dataDxfId="56">
+      <calculatedColumnFormula>INT(SUM(J3:L3)+0.0625)&amp;"m "&amp;((SUM(J3:L3)+0.0625)-INT(SUM(J3:L3)+0.0625))*16&amp;"px"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B429005B-3C2A-4B29-BC01-522C8E5715A5}" name="生物窒息高度" dataDxfId="43">
+    <tableColumn id="5" xr3:uid="{A79C77AB-332C-4A15-ACFD-BB9B8E6B2E05}" name="生物窒息高度" dataDxfId="55">
       <calculatedColumnFormula>SUM(J3:K3)+M3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{52A6878A-9E03-4079-BD2A-D65774A088C3}" name="矿车(A)2" dataDxfId="42"/>
-    <tableColumn id="11" xr3:uid="{53922683-A52C-4BB1-8910-A8475D84622A}" name="船/竹筏(B)2" dataDxfId="41"/>
-    <tableColumn id="12" xr3:uid="{A29EB1E0-DDBB-4484-A5E5-D5BB3182F6F2}" name="生物(C)2" dataDxfId="40"/>
-    <tableColumn id="13" xr3:uid="{4547FA66-A0F5-4A59-A7D1-7C2E362EC1FF}" name="生物视高" dataDxfId="39"/>
+    <tableColumn id="10" xr3:uid="{D2760891-ECED-418D-992A-272FD57402D5}" name="矿车(A)2" dataDxfId="54"/>
+    <tableColumn id="11" xr3:uid="{85C84BFC-4C27-47F4-8C56-247443488509}" name="船/竹筏(B)2" dataDxfId="53"/>
+    <tableColumn id="12" xr3:uid="{D713370E-119E-4321-B744-2A47B1781AB7}" name="生物(C)2" dataDxfId="52"/>
+    <tableColumn id="13" xr3:uid="{E24A8876-FD36-497F-B5EA-E360001E9E02}" name="生物视高" dataDxfId="51"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{27945CDA-254B-4AA6-84AD-AE71E61FA140}" name="表7_2" displayName="表7_2" ref="A2:M36" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{ECBC2B67-FC40-458D-A11A-81B8166D56F6}" name="表7" displayName="表7" ref="A2:M37" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
+  <autoFilter ref="A2:M37" xr:uid="{ECBC2B67-FC40-458D-A11A-81B8166D56F6}"/>
+  <tableColumns count="13">
+    <tableColumn id="2" xr3:uid="{1A5B9393-745A-40B5-99A3-4C560CC7B2F3}" name="组合编号" dataDxfId="48"/>
+    <tableColumn id="15" xr3:uid="{3B8A2C49-42F1-4867-BF42-2822CDF5E16D}" name="矿车(A)" dataDxfId="47"/>
+    <tableColumn id="3" xr3:uid="{48622B21-7452-4541-82EE-988C88AE65A7}" name="船/竹筏(B)" dataDxfId="46"/>
+    <tableColumn id="4" xr3:uid="{3ABEA036-6A6C-45C5-AA84-DA2D9F697B3D}" name="生物(C)" dataDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{33D96CCA-ACD8-46A8-A267-E02365DAC666}" name="无轨视高" dataDxfId="44">
+      <calculatedColumnFormula>SUM(J3:L3)+1.62</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{598FE69C-AF3A-46F1-AA80-7BF4B0C020CC}" name="有轨视高" dataDxfId="43">
+      <calculatedColumnFormula>SUM(J3:L3)+0.0625+1.62</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{F66481C1-D9A2-4C5D-B8A5-F66D7C951622}" name="无轨高度" dataDxfId="42">
+      <calculatedColumnFormula>SUM(J3:L3)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{F4B5C6C8-A44A-4E9B-84C0-2F1A0C1E9F82}" name="有轨高度" dataDxfId="41">
+      <calculatedColumnFormula>SUM(J3:L3)+0.0625</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{B429005B-3C2A-4B29-BC01-522C8E5715A5}" name="生物窒息高度" dataDxfId="40">
+      <calculatedColumnFormula>SUM(J3:K3)+M3</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{52A6878A-9E03-4079-BD2A-D65774A088C3}" name="矿车(A)2" dataDxfId="39"/>
+    <tableColumn id="11" xr3:uid="{53922683-A52C-4BB1-8910-A8475D84622A}" name="船/竹筏(B)2" dataDxfId="38"/>
+    <tableColumn id="12" xr3:uid="{A29EB1E0-DDBB-4484-A5E5-D5BB3182F6F2}" name="生物(C)2" dataDxfId="37"/>
+    <tableColumn id="13" xr3:uid="{4547FA66-A0F5-4A59-A7D1-7C2E362EC1FF}" name="生物视高" dataDxfId="36"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0D204038-0756-4564-B151-2B9567A47A25}" name="表7_24" displayName="表7_24" ref="A2:M36" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
   <autoFilter ref="A2:M36" xr:uid="{27945CDA-254B-4AA6-84AD-AE71E61FA140}"/>
   <tableColumns count="13">
-    <tableColumn id="2" xr3:uid="{E3252128-2842-475D-836E-19597AAACB23}" name="组合编号" dataDxfId="36"/>
-    <tableColumn id="15" xr3:uid="{1A256CD6-F969-4F8A-BF08-782638A053C7}" name="矿车(A)" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{139D25BD-5769-4E1F-A9B3-54F4E782916C}" name="船/竹筏(B)" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{590934DE-6D63-4E32-A2BD-E6D9EEFB943B}" name="生物(C)" dataDxfId="33"/>
-    <tableColumn id="8" xr3:uid="{4205D7C0-92A8-4837-939F-E2DA06176A19}" name="无轨视高" dataDxfId="32">
+    <tableColumn id="2" xr3:uid="{71E3AFDE-E1EF-48EB-A226-652C7D1369ED}" name="组合编号" dataDxfId="33"/>
+    <tableColumn id="15" xr3:uid="{2D9E2A5A-60D2-43EA-9A05-9F75861AA009}" name="矿车(A)" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{760FA158-F887-4326-B47C-92E490F67D50}" name="船/竹筏(B)" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{001C7352-6C93-456E-8F0C-A3A0F9ADF2B0}" name="生物(C)" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{9EEC54D2-02E5-494F-B896-BEDED7E09D17}" name="无轨视高" dataDxfId="29">
+      <calculatedColumnFormula>INT(SUM(J3:L3)+1.62)&amp;"m "&amp;((SUM(J3:L3)+1.62)-INT(SUM(J3:L3)+1.62))*16&amp;"px"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{AE11D3FC-BAAE-46BC-846B-D78E065D710A}" name="有轨视高" dataDxfId="28">
+      <calculatedColumnFormula>INT(SUM(J3:L3)+0.0625+1.62)&amp;"m "&amp;((SUM(J3:L3)+0.0625+1.62)-INT(SUM(J3:L3)+0.0625+1.62))*16&amp;"px"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{049640C2-6E76-4794-8267-3C79E3B9FB9E}" name="无轨高度" dataDxfId="27">
+      <calculatedColumnFormula>INT(SUM(J3:L3))&amp;"m "&amp;((SUM(J3:L3))-INT(SUM(J3:L3)))*16&amp;"px"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{57B1C658-DCA8-4E48-BF5C-F752585B483F}" name="有轨高度" dataDxfId="26">
+      <calculatedColumnFormula>INT(SUM(J3:L3)+0.0625)&amp;"m "&amp;((SUM(J3:L3)+0.0625)-INT(SUM(J3:L3)+0.0625))*16&amp;"px"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{911BBDC5-04F5-4304-81DC-D358149928A3}" name="生物窒息高度" dataDxfId="25">
+      <calculatedColumnFormula>SUM(J3:K3)+M3</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{6272152D-6FB1-471F-813E-31616DD66D07}" name="矿车(A)2" dataDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{1E8474CC-D3FA-458D-A233-D3147C29E74F}" name="船/竹筏(B)2" dataDxfId="23"/>
+    <tableColumn id="12" xr3:uid="{BE69942E-4AB4-4CDE-B3FA-79058FCD3C64}" name="生物(C)2" dataDxfId="22"/>
+    <tableColumn id="13" xr3:uid="{6B2C6DD5-6298-491E-84EF-95C5DE2AA271}" name="生物视高" dataDxfId="21"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{27945CDA-254B-4AA6-84AD-AE71E61FA140}" name="表7_2" displayName="表7_2" ref="A2:M36" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+  <autoFilter ref="A2:M36" xr:uid="{27945CDA-254B-4AA6-84AD-AE71E61FA140}"/>
+  <tableColumns count="13">
+    <tableColumn id="2" xr3:uid="{E3252128-2842-475D-836E-19597AAACB23}" name="组合编号" dataDxfId="18"/>
+    <tableColumn id="15" xr3:uid="{1A256CD6-F969-4F8A-BF08-782638A053C7}" name="矿车(A)" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{139D25BD-5769-4E1F-A9B3-54F4E782916C}" name="船/竹筏(B)" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{590934DE-6D63-4E32-A2BD-E6D9EEFB943B}" name="生物(C)" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{4205D7C0-92A8-4837-939F-E2DA06176A19}" name="无轨视高" dataDxfId="14">
       <calculatedColumnFormula>SUM(J3:L3)+1.62</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{67B3BB23-165B-4512-8ECD-5E32DF8E967C}" name="有轨视高" dataDxfId="31">
+    <tableColumn id="9" xr3:uid="{67B3BB23-165B-4512-8ECD-5E32DF8E967C}" name="有轨视高" dataDxfId="13">
       <calculatedColumnFormula>SUM(J3:L3)+0.0625+1.62</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{C1854081-3CCD-47A4-8AC7-A6D4D09865AF}" name="无轨高度" dataDxfId="30">
+    <tableColumn id="6" xr3:uid="{C1854081-3CCD-47A4-8AC7-A6D4D09865AF}" name="无轨高度" dataDxfId="12">
       <calculatedColumnFormula>SUM(J3:L3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{C13933C2-8933-4303-A309-B7187722B680}" name="有轨高度" dataDxfId="29">
+    <tableColumn id="7" xr3:uid="{C13933C2-8933-4303-A309-B7187722B680}" name="有轨高度" dataDxfId="11">
       <calculatedColumnFormula>SUM(J3:L3)+0.0625</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{A1FEBA74-5381-4FEA-B4CA-A6B60B7AF7D5}" name="生物窒息高度" dataDxfId="28">
+    <tableColumn id="5" xr3:uid="{A1FEBA74-5381-4FEA-B4CA-A6B60B7AF7D5}" name="生物窒息高度" dataDxfId="10">
       <calculatedColumnFormula>SUM(J3:K3)+M3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1664F24A-A49A-43FD-84D6-EA805F9ED691}" name="矿车(A)2" dataDxfId="27"/>
-    <tableColumn id="11" xr3:uid="{2AEE38F2-0B0B-4C64-923E-656338A16C44}" name="船/竹筏(B)2" dataDxfId="26"/>
-    <tableColumn id="12" xr3:uid="{44162916-A597-48D8-ABD1-2FEC989945C2}" name="生物(C)2" dataDxfId="25"/>
-    <tableColumn id="13" xr3:uid="{09CE5323-8E54-4DBC-AA57-EEF2127DE728}" name="生物视高" dataDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{1664F24A-A49A-43FD-84D6-EA805F9ED691}" name="矿车(A)2" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{2AEE38F2-0B0B-4C64-923E-656338A16C44}" name="船/竹筏(B)2" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{44162916-A597-48D8-ABD1-2FEC989945C2}" name="生物(C)2" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{09CE5323-8E54-4DBC-AA57-EEF2127DE728}" name="生物视高" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1391,6 +1755,1560 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20527DB6-DF54-42AD-8ADF-CD4B138C618C}">
+  <dimension ref="A1:O37"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.75" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.58203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.4140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.9140625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+    </row>
+    <row r="2" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="E3" s="3" t="str">
+        <f t="shared" ref="E3:E37" si="0">INT(SUM(J3:L3)+1.62)&amp;"m "&amp;((SUM(J3:L3)+1.62)-INT(SUM(J3:L3)+1.62))*16&amp;"px"</f>
+        <v>1m 9.92px</v>
+      </c>
+      <c r="F3" s="3" t="str">
+        <f t="shared" ref="F3:F37" si="1">INT(SUM(J3:L3)+0.0625+1.62)&amp;"m "&amp;((SUM(J3:L3)+0.0625+1.62)-INT(SUM(J3:L3)+0.0625+1.62))*16&amp;"px"</f>
+        <v>1m 10.92px</v>
+      </c>
+      <c r="G3" s="3" t="str">
+        <f t="shared" ref="G3:G37" si="2">INT(SUM(J3:L3))&amp;"m "&amp;((SUM(J3:L3))-INT(SUM(J3:L3)))*16&amp;"px"</f>
+        <v>0m 0px</v>
+      </c>
+      <c r="H3" s="3" t="str">
+        <f t="shared" ref="H3:H37" si="3">INT(SUM(J3:L3)+0.0625)&amp;"m "&amp;((SUM(J3:L3)+0.0625)-INT(SUM(J3:L3)+0.0625))*16&amp;"px"</f>
+        <v>0m 1px</v>
+      </c>
+      <c r="I3" s="2" t="str">
+        <f t="shared" ref="I3:I8" si="4">INT(SUM(J3:K3)+M3)&amp;"m "&amp;((SUM(J3:K3)+M3)-INT(SUM(J3:K3)+M3))*16&amp;"px"</f>
+        <v>0m 0px</v>
+      </c>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1m 3.32px</v>
+      </c>
+      <c r="F4" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>1m 4.32px</v>
+      </c>
+      <c r="G4" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>-1m 9.4px</v>
+      </c>
+      <c r="H4" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>-1m 10.4px</v>
+      </c>
+      <c r="I4" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>-1m 9.4px</v>
+      </c>
+      <c r="J4" s="6">
+        <v>-0.41249999999999998</v>
+      </c>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1m 3.32px</v>
+      </c>
+      <c r="F5" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>1m 4.32px</v>
+      </c>
+      <c r="G5" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>-1m 9.4px</v>
+      </c>
+      <c r="H5" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>-1m 10.4px</v>
+      </c>
+      <c r="I5" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>-1m 9.4px</v>
+      </c>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6">
+        <v>-0.41249999999999998</v>
+      </c>
+      <c r="L5" s="6"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1m 8.32px</v>
+      </c>
+      <c r="F6" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>1m 9.32px</v>
+      </c>
+      <c r="G6" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>-1m 14.4px</v>
+      </c>
+      <c r="H6" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>-1m 15.4px</v>
+      </c>
+      <c r="I6" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>-1m 14.4px</v>
+      </c>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="L6" s="6"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1m 6.32px</v>
+      </c>
+      <c r="F7" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>1m 7.32px</v>
+      </c>
+      <c r="G7" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>-1m 12.4px</v>
+      </c>
+      <c r="H7" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>-1m 13.4px</v>
+      </c>
+      <c r="I7" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>-1m 12.4px</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="K7" s="6">
+        <v>-0.41249999999999998</v>
+      </c>
+      <c r="L7" s="6"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1m 11.32px</v>
+      </c>
+      <c r="F8" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>1m 12.32px</v>
+      </c>
+      <c r="G8" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 1.4px</v>
+      </c>
+      <c r="H8" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 2.4px</v>
+      </c>
+      <c r="I8" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>0m 1.4px</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="K8" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="L8" s="6"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1m 14.22px</v>
+      </c>
+      <c r="F9" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>1m 15.22px</v>
+      </c>
+      <c r="G9" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 4.3px</v>
+      </c>
+      <c r="H9" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 5.3px</v>
+      </c>
+      <c r="I9" s="2" t="str">
+        <f>INT(SUM(J9:K9)+M9)&amp;"m "&amp;((SUM(J9:K9)+M9)-INT(SUM(J9:K9)+M9))*16&amp;"px"</f>
+        <v>0m 12.24px</v>
+      </c>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6">
+        <v>0.26874999999999999</v>
+      </c>
+      <c r="M9" s="6">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 2.12px</v>
+      </c>
+      <c r="F10" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 3.12px</v>
+      </c>
+      <c r="G10" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 8.2px</v>
+      </c>
+      <c r="H10" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 9.2px</v>
+      </c>
+      <c r="I10" s="2" t="str">
+        <f t="shared" ref="I10:I37" si="5">INT(SUM(J10:K10)+M10)&amp;"m "&amp;((SUM(J10:K10)+M10)-INT(SUM(J10:K10)+M10))*16&amp;"px"</f>
+        <v>1m 6.8px</v>
+      </c>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="M10" s="6">
+        <v>1.425</v>
+      </c>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 3.72px</v>
+      </c>
+      <c r="F11" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 4.72px</v>
+      </c>
+      <c r="G11" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 9.8px</v>
+      </c>
+      <c r="H11" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 10.8px</v>
+      </c>
+      <c r="I11" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>1m 8.32px</v>
+      </c>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6">
+        <v>0.61250000000000004</v>
+      </c>
+      <c r="M11" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 5.42px</v>
+      </c>
+      <c r="F12" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 6.42px</v>
+      </c>
+      <c r="G12" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 11.5px</v>
+      </c>
+      <c r="H12" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 12.5px</v>
+      </c>
+      <c r="I12" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>1m 8.32px</v>
+      </c>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6">
+        <v>0.71875</v>
+      </c>
+      <c r="M12" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 6.24px</v>
+      </c>
+      <c r="F13" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 7.24px</v>
+      </c>
+      <c r="G13" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 12.32px</v>
+      </c>
+      <c r="H13" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 13.32px</v>
+      </c>
+      <c r="I13" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>1m 12.424px</v>
+      </c>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6">
+        <v>0.77</v>
+      </c>
+      <c r="M13" s="6">
+        <v>1.7765</v>
+      </c>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 7.42px</v>
+      </c>
+      <c r="F14" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 8.42px</v>
+      </c>
+      <c r="G14" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 13.5px</v>
+      </c>
+      <c r="H14" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 14.5px</v>
+      </c>
+      <c r="I14" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>1m 8.32px</v>
+      </c>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6">
+        <v>0.84375</v>
+      </c>
+      <c r="M14" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 11.52px</v>
+      </c>
+      <c r="F15" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 12.52px</v>
+      </c>
+      <c r="G15" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 1.6px</v>
+      </c>
+      <c r="H15" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 2.6px</v>
+      </c>
+      <c r="I15" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>1m 7.12px</v>
+      </c>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M15" s="6">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>3m 0.32px</v>
+      </c>
+      <c r="F16" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>3m 1.32px</v>
+      </c>
+      <c r="G16" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 6.4px</v>
+      </c>
+      <c r="H16" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 7.4px</v>
+      </c>
+      <c r="I16" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>2m 4.4px</v>
+      </c>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="M16" s="6">
+        <v>2.2749999999999999</v>
+      </c>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 1.22px</v>
+      </c>
+      <c r="F17" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 2.22px</v>
+      </c>
+      <c r="G17" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 7.3px</v>
+      </c>
+      <c r="H17" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 8.3px</v>
+      </c>
+      <c r="I17" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>0m 15.24px</v>
+      </c>
+      <c r="J17" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6">
+        <v>0.26874999999999999</v>
+      </c>
+      <c r="M17" s="6">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 5.12px</v>
+      </c>
+      <c r="F18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 6.12px</v>
+      </c>
+      <c r="G18" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 11.2px</v>
+      </c>
+      <c r="H18" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 12.2px</v>
+      </c>
+      <c r="I18" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>1m 9.8px</v>
+      </c>
+      <c r="J18" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="M18" s="6">
+        <v>1.425</v>
+      </c>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 6.72px</v>
+      </c>
+      <c r="F19" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 7.72px</v>
+      </c>
+      <c r="G19" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 12.8px</v>
+      </c>
+      <c r="H19" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 13.8px</v>
+      </c>
+      <c r="I19" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>1m 11.32px</v>
+      </c>
+      <c r="J19" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6">
+        <v>0.61250000000000004</v>
+      </c>
+      <c r="M19" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1m 5.42px</v>
+      </c>
+      <c r="F20" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>1m 6.42px</v>
+      </c>
+      <c r="G20" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>-1m 11.5px</v>
+      </c>
+      <c r="H20" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>-1m 12.5px</v>
+      </c>
+      <c r="I20" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>0m 8.32px</v>
+      </c>
+      <c r="J20" s="6">
+        <v>-1</v>
+      </c>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6">
+        <v>0.71875</v>
+      </c>
+      <c r="M20" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1m 6.24px</v>
+      </c>
+      <c r="F21" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>1m 7.24px</v>
+      </c>
+      <c r="G21" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>-1m 12.32px</v>
+      </c>
+      <c r="H21" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>-1m 13.32px</v>
+      </c>
+      <c r="I21" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>0m 12.424px</v>
+      </c>
+      <c r="J21" s="6">
+        <v>-1</v>
+      </c>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6">
+        <v>0.77</v>
+      </c>
+      <c r="M21" s="6">
+        <v>1.7765</v>
+      </c>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 10.42px</v>
+      </c>
+      <c r="F22" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 11.42px</v>
+      </c>
+      <c r="G22" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 0.5px</v>
+      </c>
+      <c r="H22" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 1.5px</v>
+      </c>
+      <c r="I22" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>1m 11.32px</v>
+      </c>
+      <c r="J22" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6">
+        <v>0.84375</v>
+      </c>
+      <c r="M22" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 15.52px</v>
+      </c>
+      <c r="F23" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>3m 0.520000000000003px</v>
+      </c>
+      <c r="G23" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 5.6px</v>
+      </c>
+      <c r="H23" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 6.6px</v>
+      </c>
+      <c r="I23" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>1m 11.12px</v>
+      </c>
+      <c r="J23" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M23" s="6">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>3m 3.32px</v>
+      </c>
+      <c r="F24" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>3m 4.32px</v>
+      </c>
+      <c r="G24" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 9.4px</v>
+      </c>
+      <c r="H24" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 10.4px</v>
+      </c>
+      <c r="I24" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>2m 7.4px</v>
+      </c>
+      <c r="J24" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="M24" s="6">
+        <v>2.2749999999999999</v>
+      </c>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>5m 11.32px</v>
+      </c>
+      <c r="F25" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>5m 12.32px</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>4m 1.40000000000001px</v>
+      </c>
+      <c r="H25" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>4m 2.40000000000001px</v>
+      </c>
+      <c r="I25" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>3m 4.6px</v>
+      </c>
+      <c r="J25" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="M25" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>22</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 1.22px</v>
+      </c>
+      <c r="F26" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 2.22px</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 7.3px</v>
+      </c>
+      <c r="H26" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 8.3px</v>
+      </c>
+      <c r="I26" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>0m 15.24px</v>
+      </c>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="L26" s="6">
+        <v>0.26874999999999999</v>
+      </c>
+      <c r="M26" s="6">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>23</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 9.24px</v>
+      </c>
+      <c r="F27" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 10.24px</v>
+      </c>
+      <c r="G27" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 15.32px</v>
+      </c>
+      <c r="H27" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 0.32px</v>
+      </c>
+      <c r="I27" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>1m 15.424px</v>
+      </c>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="L27" s="6">
+        <v>0.77</v>
+      </c>
+      <c r="M27" s="6">
+        <v>1.7765</v>
+      </c>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>24</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 14.52px</v>
+      </c>
+      <c r="F28" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 15.52px</v>
+      </c>
+      <c r="G28" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 4.6px</v>
+      </c>
+      <c r="H28" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 5.6px</v>
+      </c>
+      <c r="I28" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>1m 10.12px</v>
+      </c>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="L28" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M28" s="6">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>25</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E29" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 6.22px</v>
+      </c>
+      <c r="F29" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 7.22px</v>
+      </c>
+      <c r="G29" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 12.3px</v>
+      </c>
+      <c r="H29" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 13.3px</v>
+      </c>
+      <c r="I29" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>1m 4.24px</v>
+      </c>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="L29" s="6">
+        <v>0.26874999999999999</v>
+      </c>
+      <c r="M29" s="6">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <v>26</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 14.24px</v>
+      </c>
+      <c r="F30" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 15.24px</v>
+      </c>
+      <c r="G30" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 4.32px</v>
+      </c>
+      <c r="H30" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 5.32px</v>
+      </c>
+      <c r="I30" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>2m 4.424px</v>
+      </c>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="L30" s="6">
+        <v>0.77</v>
+      </c>
+      <c r="M30" s="6">
+        <v>1.7765</v>
+      </c>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <v>27</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>3m 3.52px</v>
+      </c>
+      <c r="F31" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>3m 4.52px</v>
+      </c>
+      <c r="G31" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 9.6px</v>
+      </c>
+      <c r="H31" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 10.6px</v>
+      </c>
+      <c r="I31" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>1m 15.12px</v>
+      </c>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="L31" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M31" s="6">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E32" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 4.22px</v>
+      </c>
+      <c r="F32" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 5.22px</v>
+      </c>
+      <c r="G32" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 10.3px</v>
+      </c>
+      <c r="H32" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 11.3px</v>
+      </c>
+      <c r="I32" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>1m 2.24px</v>
+      </c>
+      <c r="J32" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="K32" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="L32" s="6">
+        <v>0.26874999999999999</v>
+      </c>
+      <c r="M32" s="6">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 12.24px</v>
+      </c>
+      <c r="F33" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 13.24px</v>
+      </c>
+      <c r="G33" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 2.32px</v>
+      </c>
+      <c r="H33" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 3.32px</v>
+      </c>
+      <c r="I33" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>2m 2.424px</v>
+      </c>
+      <c r="J33" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="K33" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="L33" s="6">
+        <v>0.77</v>
+      </c>
+      <c r="M33" s="6">
+        <v>1.7765</v>
+      </c>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <v>30</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>3m 1.52px</v>
+      </c>
+      <c r="F34" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>3m 2.52px</v>
+      </c>
+      <c r="G34" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 7.6px</v>
+      </c>
+      <c r="H34" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 8.6px</v>
+      </c>
+      <c r="I34" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>1m 13.12px</v>
+      </c>
+      <c r="J34" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="K34" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="L34" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M34" s="6">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <v>31</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 9.22px</v>
+      </c>
+      <c r="F35" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 10.22px</v>
+      </c>
+      <c r="G35" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 15.3px</v>
+      </c>
+      <c r="H35" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 0.300000000000001px</v>
+      </c>
+      <c r="I35" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>1m 7.24px</v>
+      </c>
+      <c r="J35" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="K35" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="L35" s="6">
+        <v>0.26874999999999999</v>
+      </c>
+      <c r="M35" s="6">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <v>32</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>3m 1.24px</v>
+      </c>
+      <c r="F36" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>3m 2.24px</v>
+      </c>
+      <c r="G36" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 7.32px</v>
+      </c>
+      <c r="H36" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 8.32px</v>
+      </c>
+      <c r="I36" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>2m 7.424px</v>
+      </c>
+      <c r="J36" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="K36" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="L36" s="6">
+        <v>0.77</v>
+      </c>
+      <c r="M36" s="6">
+        <v>1.7765</v>
+      </c>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <v>33</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>3m 6.52px</v>
+      </c>
+      <c r="F37" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>3m 7.52px</v>
+      </c>
+      <c r="G37" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 12.6px</v>
+      </c>
+      <c r="H37" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 13.6px</v>
+      </c>
+      <c r="I37" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>2m 2.12px</v>
+      </c>
+      <c r="J37" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="K37" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="L37" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M37" s="6">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="J1:M1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C1B65AC-A9AA-48F8-B54F-CBEF804346E2}">
   <dimension ref="A1:O37"/>
   <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -1412,25 +3330,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="13" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
       <c r="I1" s="8"/>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
     </row>
@@ -1481,19 +3399,19 @@
       </c>
       <c r="B3" s="2"/>
       <c r="E3" s="3">
-        <f>SUM(J3:L3)+1.62</f>
+        <f t="shared" ref="E3:E37" si="0">SUM(J3:L3)+1.62</f>
         <v>1.62</v>
       </c>
       <c r="F3" s="3">
-        <f>SUM(J3:L3)+0.0625+1.62</f>
+        <f t="shared" ref="F3:F37" si="1">SUM(J3:L3)+0.0625+1.62</f>
         <v>1.6825000000000001</v>
       </c>
       <c r="G3" s="3">
-        <f>SUM(J3:L3)</f>
+        <f t="shared" ref="G3:G37" si="2">SUM(J3:L3)</f>
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <f>SUM(J3:L3)+0.0625</f>
+        <f t="shared" ref="H3:H37" si="3">SUM(J3:L3)+0.0625</f>
         <v>6.25E-2</v>
       </c>
       <c r="J3" s="6"/>
@@ -1510,19 +3428,19 @@
         <v>12</v>
       </c>
       <c r="E4" s="3">
-        <f>SUM(J4:L4)+1.62</f>
+        <f t="shared" si="0"/>
         <v>1.2075</v>
       </c>
       <c r="F4" s="3">
-        <f>SUM(J4:L4)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>1.27</v>
       </c>
       <c r="G4" s="3">
-        <f>SUM(J4:L4)</f>
+        <f t="shared" si="2"/>
         <v>-0.41249999999999998</v>
       </c>
       <c r="H4" s="3">
-        <f>SUM(J4:L4)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>-0.35</v>
       </c>
       <c r="J4" s="6">
@@ -1542,19 +3460,19 @@
         <v>18</v>
       </c>
       <c r="E5" s="3">
-        <f>SUM(J5:L5)+1.62</f>
+        <f t="shared" si="0"/>
         <v>1.2075</v>
       </c>
       <c r="F5" s="3">
-        <f>SUM(J5:L5)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>1.27</v>
       </c>
       <c r="G5" s="3">
-        <f>SUM(J5:L5)</f>
+        <f t="shared" si="2"/>
         <v>-0.41249999999999998</v>
       </c>
       <c r="H5" s="3">
-        <f>SUM(J5:L5)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>-0.35</v>
       </c>
       <c r="J5" s="6"/>
@@ -1573,19 +3491,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="3">
-        <f>SUM(J6:L6)+1.62</f>
+        <f t="shared" si="0"/>
         <v>1.52</v>
       </c>
       <c r="F6" s="3">
-        <f>SUM(J6:L6)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>1.5825</v>
       </c>
       <c r="G6" s="3">
-        <f>SUM(J6:L6)</f>
+        <f t="shared" si="2"/>
         <v>-0.1</v>
       </c>
       <c r="H6" s="3">
-        <f>SUM(J6:L6)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>-3.7500000000000006E-2</v>
       </c>
       <c r="J6" s="6"/>
@@ -1607,19 +3525,19 @@
         <v>18</v>
       </c>
       <c r="E7" s="3">
-        <f>SUM(J7:L7)+1.62</f>
+        <f t="shared" si="0"/>
         <v>1.395</v>
       </c>
       <c r="F7" s="3">
-        <f>SUM(J7:L7)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>1.4575</v>
       </c>
       <c r="G7" s="3">
-        <f>SUM(J7:L7)</f>
+        <f t="shared" si="2"/>
         <v>-0.22499999999999998</v>
       </c>
       <c r="H7" s="3">
-        <f>SUM(J7:L7)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>-0.16249999999999998</v>
       </c>
       <c r="I7" s="2"/>
@@ -1644,19 +3562,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="3">
-        <f>SUM(J8:L8)+1.62</f>
+        <f t="shared" si="0"/>
         <v>1.7075</v>
       </c>
       <c r="F8" s="3">
-        <f>SUM(J8:L8)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>1.77</v>
       </c>
       <c r="G8" s="3">
-        <f>SUM(J8:L8)</f>
+        <f t="shared" si="2"/>
         <v>8.7499999999999994E-2</v>
       </c>
       <c r="H8" s="3">
-        <f>SUM(J8:L8)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>0.15</v>
       </c>
       <c r="I8" s="2"/>
@@ -1678,23 +3596,23 @@
         <v>2</v>
       </c>
       <c r="E9" s="3">
-        <f>SUM(J9:L9)+1.62</f>
+        <f t="shared" si="0"/>
         <v>1.8887500000000002</v>
       </c>
       <c r="F9" s="3">
-        <f>SUM(J9:L9)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>1.9512500000000002</v>
       </c>
       <c r="G9" s="3">
-        <f>SUM(J9:L9)</f>
+        <f t="shared" si="2"/>
         <v>0.26874999999999999</v>
       </c>
       <c r="H9" s="3">
-        <f>SUM(J9:L9)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>0.33124999999999999</v>
       </c>
       <c r="I9" s="2">
-        <f>SUM(J9:K9)+M9</f>
+        <f t="shared" ref="I9:I37" si="4">SUM(J9:K9)+M9</f>
         <v>0.76500000000000001</v>
       </c>
       <c r="J9" s="6"/>
@@ -1716,23 +3634,23 @@
         <v>3</v>
       </c>
       <c r="E10" s="3">
-        <f>SUM(J10:L10)+1.62</f>
+        <f t="shared" si="0"/>
         <v>2.1325000000000003</v>
       </c>
       <c r="F10" s="3">
-        <f>SUM(J10:L10)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>2.1950000000000003</v>
       </c>
       <c r="G10" s="3">
-        <f>SUM(J10:L10)</f>
+        <f t="shared" si="2"/>
         <v>0.51249999999999996</v>
       </c>
       <c r="H10" s="3">
-        <f>SUM(J10:L10)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>0.57499999999999996</v>
       </c>
       <c r="I10" s="2">
-        <f>SUM(J10:K10)+M10</f>
+        <f t="shared" si="4"/>
         <v>1.425</v>
       </c>
       <c r="J10" s="6"/>
@@ -1754,23 +3672,23 @@
         <v>4</v>
       </c>
       <c r="E11" s="3">
-        <f>SUM(J11:L11)+1.62</f>
+        <f t="shared" si="0"/>
         <v>2.2324999999999999</v>
       </c>
       <c r="F11" s="3">
-        <f>SUM(J11:L11)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>2.2949999999999999</v>
       </c>
       <c r="G11" s="3">
-        <f>SUM(J11:L11)</f>
+        <f t="shared" si="2"/>
         <v>0.61250000000000004</v>
       </c>
       <c r="H11" s="3">
-        <f>SUM(J11:L11)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>0.67500000000000004</v>
       </c>
       <c r="I11" s="2">
-        <f>SUM(J11:K11)+M11</f>
+        <f t="shared" si="4"/>
         <v>1.52</v>
       </c>
       <c r="J11" s="6"/>
@@ -1792,23 +3710,23 @@
         <v>5</v>
       </c>
       <c r="E12" s="3">
-        <f>SUM(J12:L12)+1.62</f>
+        <f t="shared" si="0"/>
         <v>2.3387500000000001</v>
       </c>
       <c r="F12" s="3">
-        <f>SUM(J12:L12)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>2.4012500000000001</v>
       </c>
       <c r="G12" s="3">
-        <f>SUM(J12:L12)</f>
+        <f t="shared" si="2"/>
         <v>0.71875</v>
       </c>
       <c r="H12" s="3">
-        <f>SUM(J12:L12)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>0.78125</v>
       </c>
       <c r="I12" s="2">
-        <f>SUM(J12:K12)+M12</f>
+        <f t="shared" si="4"/>
         <v>1.52</v>
       </c>
       <c r="J12" s="6"/>
@@ -1830,23 +3748,23 @@
         <v>6</v>
       </c>
       <c r="E13" s="3">
-        <f>SUM(J13:L13)+1.62</f>
+        <f t="shared" si="0"/>
         <v>2.39</v>
       </c>
       <c r="F13" s="3">
-        <f>SUM(J13:L13)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>2.4525000000000001</v>
       </c>
       <c r="G13" s="3">
-        <f>SUM(J13:L13)</f>
+        <f t="shared" si="2"/>
         <v>0.77</v>
       </c>
       <c r="H13" s="3">
-        <f>SUM(J13:L13)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>0.83250000000000002</v>
       </c>
       <c r="I13" s="2">
-        <f>SUM(J13:K13)+M13</f>
+        <f t="shared" si="4"/>
         <v>1.7765</v>
       </c>
       <c r="J13" s="6"/>
@@ -1868,23 +3786,23 @@
         <v>7</v>
       </c>
       <c r="E14" s="3">
-        <f>SUM(J14:L14)+1.62</f>
+        <f t="shared" si="0"/>
         <v>2.4637500000000001</v>
       </c>
       <c r="F14" s="3">
-        <f>SUM(J14:L14)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>2.5262500000000001</v>
       </c>
       <c r="G14" s="3">
-        <f>SUM(J14:L14)</f>
+        <f t="shared" si="2"/>
         <v>0.84375</v>
       </c>
       <c r="H14" s="3">
-        <f>SUM(J14:L14)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>0.90625</v>
       </c>
       <c r="I14" s="2">
-        <f>SUM(J14:K14)+M14</f>
+        <f t="shared" si="4"/>
         <v>1.52</v>
       </c>
       <c r="J14" s="6"/>
@@ -1906,23 +3824,23 @@
         <v>16</v>
       </c>
       <c r="E15" s="3">
-        <f>SUM(J15:L15)+1.62</f>
+        <f t="shared" si="0"/>
         <v>2.72</v>
       </c>
       <c r="F15" s="3">
-        <f>SUM(J15:L15)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>2.7825000000000002</v>
       </c>
       <c r="G15" s="3">
-        <f>SUM(J15:L15)</f>
+        <f t="shared" si="2"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="H15" s="3">
-        <f>SUM(J15:L15)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>1.1625000000000001</v>
       </c>
       <c r="I15" s="2">
-        <f>SUM(J15:K15)+M15</f>
+        <f t="shared" si="4"/>
         <v>1.4450000000000001</v>
       </c>
       <c r="J15" s="6"/>
@@ -1944,23 +3862,23 @@
         <v>8</v>
       </c>
       <c r="E16" s="3">
-        <f>SUM(J16:L16)+1.62</f>
+        <f t="shared" si="0"/>
         <v>3.02</v>
       </c>
       <c r="F16" s="3">
-        <f>SUM(J16:L16)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>3.0825</v>
       </c>
       <c r="G16" s="3">
-        <f>SUM(J16:L16)</f>
+        <f t="shared" si="2"/>
         <v>1.4</v>
       </c>
       <c r="H16" s="3">
-        <f>SUM(J16:L16)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>1.4624999999999999</v>
       </c>
       <c r="I16" s="2">
-        <f>SUM(J16:K16)+M16</f>
+        <f t="shared" si="4"/>
         <v>2.2749999999999999</v>
       </c>
       <c r="J16" s="6"/>
@@ -1985,23 +3903,23 @@
         <v>2</v>
       </c>
       <c r="E17" s="3">
-        <f>SUM(J17:L17)+1.62</f>
+        <f t="shared" si="0"/>
         <v>2.0762499999999999</v>
       </c>
       <c r="F17" s="3">
-        <f>SUM(J17:L17)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>2.1387499999999999</v>
       </c>
       <c r="G17" s="3">
-        <f>SUM(J17:L17)</f>
+        <f t="shared" si="2"/>
         <v>0.45624999999999999</v>
       </c>
       <c r="H17" s="3">
-        <f>SUM(J17:L17)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>0.51875000000000004</v>
       </c>
       <c r="I17" s="2">
-        <f>SUM(J17:K17)+M17</f>
+        <f t="shared" si="4"/>
         <v>0.95250000000000001</v>
       </c>
       <c r="J17" s="6">
@@ -2028,23 +3946,23 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
-        <f>SUM(J18:L18)+1.62</f>
+        <f t="shared" si="0"/>
         <v>2.3200000000000003</v>
       </c>
       <c r="F18" s="3">
-        <f>SUM(J18:L18)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>2.3825000000000003</v>
       </c>
       <c r="G18" s="3">
-        <f>SUM(J18:L18)</f>
+        <f t="shared" si="2"/>
         <v>0.7</v>
       </c>
       <c r="H18" s="3">
-        <f>SUM(J18:L18)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>0.76249999999999996</v>
       </c>
       <c r="I18" s="2">
-        <f>SUM(J18:K18)+M18</f>
+        <f t="shared" si="4"/>
         <v>1.6125</v>
       </c>
       <c r="J18" s="6">
@@ -2071,23 +3989,23 @@
         <v>4</v>
       </c>
       <c r="E19" s="3">
-        <f>SUM(J19:L19)+1.62</f>
+        <f t="shared" si="0"/>
         <v>2.42</v>
       </c>
       <c r="F19" s="3">
-        <f>SUM(J19:L19)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>2.4824999999999999</v>
       </c>
       <c r="G19" s="3">
-        <f>SUM(J19:L19)</f>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
       <c r="H19" s="3">
-        <f>SUM(J19:L19)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>0.86250000000000004</v>
       </c>
       <c r="I19" s="2">
-        <f>SUM(J19:K19)+M19</f>
+        <f t="shared" si="4"/>
         <v>1.7075</v>
       </c>
       <c r="J19" s="6">
@@ -2114,23 +4032,23 @@
         <v>5</v>
       </c>
       <c r="E20" s="3">
-        <f>SUM(J20:L20)+1.62</f>
+        <f t="shared" si="0"/>
         <v>1.3387500000000001</v>
       </c>
       <c r="F20" s="3">
-        <f>SUM(J20:L20)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>1.4012500000000001</v>
       </c>
       <c r="G20" s="3">
-        <f>SUM(J20:L20)</f>
+        <f t="shared" si="2"/>
         <v>-0.28125</v>
       </c>
       <c r="H20" s="3">
-        <f>SUM(J20:L20)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>-0.21875</v>
       </c>
       <c r="I20" s="2">
-        <f>SUM(J20:K20)+M20</f>
+        <f t="shared" si="4"/>
         <v>0.52</v>
       </c>
       <c r="J20" s="6">
@@ -2157,23 +4075,23 @@
         <v>6</v>
       </c>
       <c r="E21" s="3">
-        <f>SUM(J21:L21)+1.62</f>
+        <f t="shared" si="0"/>
         <v>1.3900000000000001</v>
       </c>
       <c r="F21" s="3">
-        <f>SUM(J21:L21)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>1.4525000000000001</v>
       </c>
       <c r="G21" s="3">
-        <f>SUM(J21:L21)</f>
+        <f t="shared" si="2"/>
         <v>-0.22999999999999998</v>
       </c>
       <c r="H21" s="3">
-        <f>SUM(J21:L21)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>-0.16749999999999998</v>
       </c>
       <c r="I21" s="2">
-        <f>SUM(J21:K21)+M21</f>
+        <f t="shared" si="4"/>
         <v>0.77649999999999997</v>
       </c>
       <c r="J21" s="6">
@@ -2200,23 +4118,23 @@
         <v>7</v>
       </c>
       <c r="E22" s="3">
-        <f>SUM(J22:L22)+1.62</f>
+        <f t="shared" si="0"/>
         <v>2.6512500000000001</v>
       </c>
       <c r="F22" s="3">
-        <f>SUM(J22:L22)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>2.7137500000000001</v>
       </c>
       <c r="G22" s="3">
-        <f>SUM(J22:L22)</f>
+        <f t="shared" si="2"/>
         <v>1.03125</v>
       </c>
       <c r="H22" s="3">
-        <f>SUM(J22:L22)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>1.09375</v>
       </c>
       <c r="I22" s="2">
-        <f>SUM(J22:K22)+M22</f>
+        <f t="shared" si="4"/>
         <v>1.7075</v>
       </c>
       <c r="J22" s="6">
@@ -2243,23 +4161,23 @@
         <v>16</v>
       </c>
       <c r="E23" s="3">
-        <f>SUM(J23:L23)+1.62</f>
+        <f t="shared" si="0"/>
         <v>2.97</v>
       </c>
       <c r="F23" s="3">
-        <f>SUM(J23:L23)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>3.0325000000000002</v>
       </c>
       <c r="G23" s="3">
-        <f>SUM(J23:L23)</f>
+        <f t="shared" si="2"/>
         <v>1.35</v>
       </c>
       <c r="H23" s="3">
-        <f>SUM(J23:L23)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>1.4125000000000001</v>
       </c>
       <c r="I23" s="2">
-        <f>SUM(J23:K23)+M23</f>
+        <f t="shared" si="4"/>
         <v>1.6950000000000001</v>
       </c>
       <c r="J23" s="6">
@@ -2286,23 +4204,23 @@
         <v>8</v>
       </c>
       <c r="E24" s="3">
-        <f>SUM(J24:L24)+1.62</f>
+        <f t="shared" si="0"/>
         <v>3.2075</v>
       </c>
       <c r="F24" s="3">
-        <f>SUM(J24:L24)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>3.27</v>
       </c>
       <c r="G24" s="3">
-        <f>SUM(J24:L24)</f>
+        <f t="shared" si="2"/>
         <v>1.5874999999999999</v>
       </c>
       <c r="H24" s="3">
-        <f>SUM(J24:L24)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>1.65</v>
       </c>
       <c r="I24" s="2">
-        <f>SUM(J24:K24)+M24</f>
+        <f t="shared" si="4"/>
         <v>2.4624999999999999</v>
       </c>
       <c r="J24" s="6">
@@ -2328,23 +4246,23 @@
         <v>41</v>
       </c>
       <c r="E25" s="3">
-        <f>SUM(J25:L25)+1.62</f>
+        <f t="shared" si="0"/>
         <v>5.7075000000000005</v>
       </c>
       <c r="F25" s="3">
-        <f>SUM(J25:L25)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>5.7700000000000005</v>
       </c>
       <c r="G25" s="3">
-        <f>SUM(J25:L25)</f>
+        <f t="shared" si="2"/>
         <v>4.0875000000000004</v>
       </c>
       <c r="H25" s="3">
-        <f>SUM(J25:L25)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>4.1500000000000004</v>
       </c>
       <c r="I25" s="2">
-        <f>SUM(J25:K25)+M25</f>
+        <f t="shared" si="4"/>
         <v>3.2875000000000001</v>
       </c>
       <c r="J25" s="6">
@@ -2371,23 +4289,23 @@
         <v>2</v>
       </c>
       <c r="E26" s="3">
-        <f>SUM(J26:L26)+1.62</f>
+        <f t="shared" si="0"/>
         <v>2.0762499999999999</v>
       </c>
       <c r="F26" s="3">
-        <f>SUM(J26:L26)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>2.1387499999999999</v>
       </c>
       <c r="G26" s="3">
-        <f>SUM(J26:L26)</f>
+        <f t="shared" si="2"/>
         <v>0.45624999999999999</v>
       </c>
       <c r="H26" s="3">
-        <f>SUM(J26:L26)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>0.51875000000000004</v>
       </c>
       <c r="I26" s="2">
-        <f>SUM(J26:K26)+M26</f>
+        <f t="shared" si="4"/>
         <v>0.95250000000000001</v>
       </c>
       <c r="J26" s="6"/>
@@ -2414,23 +4332,23 @@
         <v>21</v>
       </c>
       <c r="E27" s="3">
-        <f>SUM(J27:L27)+1.62</f>
+        <f t="shared" si="0"/>
         <v>2.5775000000000001</v>
       </c>
       <c r="F27" s="3">
-        <f>SUM(J27:L27)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>2.64</v>
       </c>
       <c r="G27" s="3">
-        <f>SUM(J27:L27)</f>
+        <f t="shared" si="2"/>
         <v>0.95750000000000002</v>
       </c>
       <c r="H27" s="3">
-        <f>SUM(J27:L27)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>1.02</v>
       </c>
       <c r="I27" s="2">
-        <f>SUM(J27:K27)+M27</f>
+        <f t="shared" si="4"/>
         <v>1.964</v>
       </c>
       <c r="J27" s="6"/>
@@ -2457,23 +4375,23 @@
         <v>20</v>
       </c>
       <c r="E28" s="3">
-        <f>SUM(J28:L28)+1.62</f>
+        <f t="shared" si="0"/>
         <v>2.9075000000000002</v>
       </c>
       <c r="F28" s="3">
-        <f>SUM(J28:L28)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>2.97</v>
       </c>
       <c r="G28" s="3">
-        <f>SUM(J28:L28)</f>
+        <f t="shared" si="2"/>
         <v>1.2875000000000001</v>
       </c>
       <c r="H28" s="3">
-        <f>SUM(J28:L28)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>1.35</v>
       </c>
       <c r="I28" s="2">
-        <f>SUM(J28:K28)+M28</f>
+        <f t="shared" si="4"/>
         <v>1.6325000000000001</v>
       </c>
       <c r="J28" s="6"/>
@@ -2500,23 +4418,23 @@
         <v>2</v>
       </c>
       <c r="E29" s="3">
-        <f>SUM(J29:L29)+1.62</f>
+        <f t="shared" si="0"/>
         <v>2.3887499999999999</v>
       </c>
       <c r="F29" s="3">
-        <f>SUM(J29:L29)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>2.4512499999999999</v>
       </c>
       <c r="G29" s="3">
-        <f>SUM(J29:L29)</f>
+        <f t="shared" si="2"/>
         <v>0.76875000000000004</v>
       </c>
       <c r="H29" s="3">
-        <f>SUM(J29:L29)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>0.83125000000000004</v>
       </c>
       <c r="I29" s="2">
-        <f>SUM(J29:K29)+M29</f>
+        <f t="shared" si="4"/>
         <v>1.2650000000000001</v>
       </c>
       <c r="J29" s="6"/>
@@ -2543,23 +4461,23 @@
         <v>6</v>
       </c>
       <c r="E30" s="3">
-        <f>SUM(J30:L30)+1.62</f>
+        <f t="shared" si="0"/>
         <v>2.89</v>
       </c>
       <c r="F30" s="3">
-        <f>SUM(J30:L30)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>2.9525000000000001</v>
       </c>
       <c r="G30" s="3">
-        <f>SUM(J30:L30)</f>
+        <f t="shared" si="2"/>
         <v>1.27</v>
       </c>
       <c r="H30" s="3">
-        <f>SUM(J30:L30)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>1.3325</v>
       </c>
       <c r="I30" s="2">
-        <f>SUM(J30:K30)+M30</f>
+        <f t="shared" si="4"/>
         <v>2.2765</v>
       </c>
       <c r="J30" s="6"/>
@@ -2586,23 +4504,23 @@
         <v>20</v>
       </c>
       <c r="E31" s="3">
-        <f>SUM(J31:L31)+1.62</f>
+        <f t="shared" si="0"/>
         <v>3.22</v>
       </c>
       <c r="F31" s="3">
-        <f>SUM(J31:L31)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>3.2825000000000002</v>
       </c>
       <c r="G31" s="3">
-        <f>SUM(J31:L31)</f>
+        <f t="shared" si="2"/>
         <v>1.6</v>
       </c>
       <c r="H31" s="3">
-        <f>SUM(J31:L31)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>1.6625000000000001</v>
       </c>
       <c r="I31" s="2">
-        <f>SUM(J31:K31)+M31</f>
+        <f t="shared" si="4"/>
         <v>1.9450000000000001</v>
       </c>
       <c r="J31" s="6"/>
@@ -2632,23 +4550,23 @@
         <v>2</v>
       </c>
       <c r="E32" s="3">
-        <f>SUM(J32:L32)+1.62</f>
+        <f t="shared" si="0"/>
         <v>2.2637499999999999</v>
       </c>
       <c r="F32" s="3">
-        <f>SUM(J32:L32)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>2.3262499999999999</v>
       </c>
       <c r="G32" s="3">
-        <f>SUM(J32:L32)</f>
+        <f t="shared" si="2"/>
         <v>0.64375000000000004</v>
       </c>
       <c r="H32" s="3">
-        <f>SUM(J32:L32)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>0.70625000000000004</v>
       </c>
       <c r="I32" s="2">
-        <f>SUM(J32:K32)+M32</f>
+        <f t="shared" si="4"/>
         <v>1.1400000000000001</v>
       </c>
       <c r="J32" s="6">
@@ -2680,23 +4598,23 @@
         <v>21</v>
       </c>
       <c r="E33" s="3">
-        <f>SUM(J33:L33)+1.62</f>
+        <f t="shared" si="0"/>
         <v>2.7650000000000001</v>
       </c>
       <c r="F33" s="3">
-        <f>SUM(J33:L33)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>2.8275000000000001</v>
       </c>
       <c r="G33" s="3">
-        <f>SUM(J33:L33)</f>
+        <f t="shared" si="2"/>
         <v>1.145</v>
       </c>
       <c r="H33" s="3">
-        <f>SUM(J33:L33)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>1.2075</v>
       </c>
       <c r="I33" s="2">
-        <f>SUM(J33:K33)+M33</f>
+        <f t="shared" si="4"/>
         <v>2.1515</v>
       </c>
       <c r="J33" s="6">
@@ -2728,23 +4646,23 @@
         <v>20</v>
       </c>
       <c r="E34" s="3">
-        <f>SUM(J34:L34)+1.62</f>
+        <f t="shared" si="0"/>
         <v>3.0950000000000002</v>
       </c>
       <c r="F34" s="3">
-        <f>SUM(J34:L34)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>3.1575000000000002</v>
       </c>
       <c r="G34" s="3">
-        <f>SUM(J34:L34)</f>
+        <f t="shared" si="2"/>
         <v>1.4750000000000001</v>
       </c>
       <c r="H34" s="3">
-        <f>SUM(J34:L34)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>1.5375000000000001</v>
       </c>
       <c r="I34" s="2">
-        <f>SUM(J34:K34)+M34</f>
+        <f t="shared" si="4"/>
         <v>1.82</v>
       </c>
       <c r="J34" s="6">
@@ -2776,23 +4694,23 @@
         <v>2</v>
       </c>
       <c r="E35" s="3">
-        <f>SUM(J35:L35)+1.62</f>
+        <f t="shared" si="0"/>
         <v>2.5762499999999999</v>
       </c>
       <c r="F35" s="3">
-        <f>SUM(J35:L35)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>2.6387499999999999</v>
       </c>
       <c r="G35" s="3">
-        <f>SUM(J35:L35)</f>
+        <f t="shared" si="2"/>
         <v>0.95625000000000004</v>
       </c>
       <c r="H35" s="3">
-        <f>SUM(J35:L35)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>1.01875</v>
       </c>
       <c r="I35" s="2">
-        <f>SUM(J35:K35)+M35</f>
+        <f t="shared" si="4"/>
         <v>1.4525000000000001</v>
       </c>
       <c r="J35" s="6">
@@ -2824,23 +4742,23 @@
         <v>6</v>
       </c>
       <c r="E36" s="3">
-        <f>SUM(J36:L36)+1.62</f>
+        <f t="shared" si="0"/>
         <v>3.0775000000000001</v>
       </c>
       <c r="F36" s="3">
-        <f>SUM(J36:L36)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>3.14</v>
       </c>
       <c r="G36" s="3">
-        <f>SUM(J36:L36)</f>
+        <f t="shared" si="2"/>
         <v>1.4575</v>
       </c>
       <c r="H36" s="3">
-        <f>SUM(J36:L36)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>1.52</v>
       </c>
       <c r="I36" s="2">
-        <f>SUM(J36:K36)+M36</f>
+        <f t="shared" si="4"/>
         <v>2.464</v>
       </c>
       <c r="J36" s="6">
@@ -2872,23 +4790,23 @@
         <v>20</v>
       </c>
       <c r="E37" s="3">
-        <f>SUM(J37:L37)+1.62</f>
+        <f t="shared" si="0"/>
         <v>3.4075000000000002</v>
       </c>
       <c r="F37" s="3">
-        <f>SUM(J37:L37)+0.0625+1.62</f>
+        <f t="shared" si="1"/>
         <v>3.47</v>
       </c>
       <c r="G37" s="3">
-        <f>SUM(J37:L37)</f>
+        <f t="shared" si="2"/>
         <v>1.7875000000000001</v>
       </c>
       <c r="H37" s="3">
-        <f>SUM(J37:L37)+0.0625</f>
+        <f t="shared" si="3"/>
         <v>1.85</v>
       </c>
       <c r="I37" s="2">
-        <f>SUM(J37:K37)+M37</f>
+        <f t="shared" si="4"/>
         <v>2.1325000000000003</v>
       </c>
       <c r="J37" s="6">
@@ -2933,7 +4851,1495 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68667553-861F-4A4A-B49C-191C6A8BFE93}">
+  <dimension ref="A1:O36"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.58203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.4140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.9140625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+    </row>
+    <row r="2" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="E3" s="3" t="str">
+        <f t="shared" ref="E3:E36" si="0">INT(SUM(J3:L3)+1.62)&amp;"m "&amp;((SUM(J3:L3)+1.62)-INT(SUM(J3:L3)+1.62))*16&amp;"px"</f>
+        <v>1m 9.92px</v>
+      </c>
+      <c r="F3" s="3" t="str">
+        <f t="shared" ref="F3:F36" si="1">INT(SUM(J3:L3)+0.0625+1.62)&amp;"m "&amp;((SUM(J3:L3)+0.0625+1.62)-INT(SUM(J3:L3)+0.0625+1.62))*16&amp;"px"</f>
+        <v>1m 10.92px</v>
+      </c>
+      <c r="G3" s="3" t="str">
+        <f t="shared" ref="G3:G36" si="2">INT(SUM(J3:L3))&amp;"m "&amp;((SUM(J3:L3))-INT(SUM(J3:L3)))*16&amp;"px"</f>
+        <v>0m 0px</v>
+      </c>
+      <c r="H3" s="3" t="str">
+        <f t="shared" ref="H3:H36" si="3">INT(SUM(J3:L3)+0.0625)&amp;"m "&amp;((SUM(J3:L3)+0.0625)-INT(SUM(J3:L3)+0.0625))*16&amp;"px"</f>
+        <v>0m 1px</v>
+      </c>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1m 4.32px</v>
+      </c>
+      <c r="F4" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>1m 5.32px</v>
+      </c>
+      <c r="G4" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>-1m 10.4px</v>
+      </c>
+      <c r="H4" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>-1m 11.4px</v>
+      </c>
+      <c r="J4" s="6">
+        <v>-0.35</v>
+      </c>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1m 4.32px</v>
+      </c>
+      <c r="F5" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>1m 5.32px</v>
+      </c>
+      <c r="G5" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>-1m 10.4px</v>
+      </c>
+      <c r="H5" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>-1m 11.4px</v>
+      </c>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6">
+        <v>-0.35</v>
+      </c>
+      <c r="L5" s="6"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1m 8.32px</v>
+      </c>
+      <c r="F6" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>1m 9.32px</v>
+      </c>
+      <c r="G6" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>-1m 14.4px</v>
+      </c>
+      <c r="H6" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>-1m 15.4px</v>
+      </c>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="L6" s="6"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1m 4.32px</v>
+      </c>
+      <c r="F7" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>1m 5.32px</v>
+      </c>
+      <c r="G7" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>-1m 10.4px</v>
+      </c>
+      <c r="H7" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>-1m 11.4px</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="6">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6">
+        <v>-0.35</v>
+      </c>
+      <c r="L7" s="6"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>13</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1m 8.32px</v>
+      </c>
+      <c r="F8" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>1m 9.32px</v>
+      </c>
+      <c r="G8" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>-1m 14.4px</v>
+      </c>
+      <c r="H8" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>-1m 15.4px</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="6">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="L8" s="6"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1m 15.12px</v>
+      </c>
+      <c r="F9" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 0.120000000000005px</v>
+      </c>
+      <c r="G9" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 5.2px</v>
+      </c>
+      <c r="H9" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 6.2px</v>
+      </c>
+      <c r="I9" s="2" t="str">
+        <f>INT(SUM(J9:K9)+M9)&amp;"m "&amp;((SUM(J9:K9)+M9)-INT(SUM(J9:K9)+M9))*16&amp;"px"</f>
+        <v>0m 12.24px</v>
+      </c>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M9" s="6">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 2.32px</v>
+      </c>
+      <c r="F10" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 3.32px</v>
+      </c>
+      <c r="G10" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 8.4px</v>
+      </c>
+      <c r="H10" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 9.4px</v>
+      </c>
+      <c r="I10" s="2" t="str">
+        <f t="shared" ref="I10:I36" si="4">INT(SUM(J10:K10)+M10)&amp;"m "&amp;((SUM(J10:K10)+M10)-INT(SUM(J10:K10)+M10))*16&amp;"px"</f>
+        <v>1m 6.8px</v>
+      </c>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="M10" s="6">
+        <v>1.425</v>
+      </c>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>6</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 3.52px</v>
+      </c>
+      <c r="F11" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 4.52px</v>
+      </c>
+      <c r="G11" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 9.6px</v>
+      </c>
+      <c r="H11" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 10.6px</v>
+      </c>
+      <c r="I11" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>1m 8.32px</v>
+      </c>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="M11" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>7</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 4.52px</v>
+      </c>
+      <c r="F12" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 5.52px</v>
+      </c>
+      <c r="G12" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 10.6px</v>
+      </c>
+      <c r="H12" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 11.6px</v>
+      </c>
+      <c r="I12" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>1m 8.32px</v>
+      </c>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6">
+        <v>0.66249999999999998</v>
+      </c>
+      <c r="M12" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 6.27200000000001px</v>
+      </c>
+      <c r="F13" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 7.27200000000001px</v>
+      </c>
+      <c r="G13" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 12.352px</v>
+      </c>
+      <c r="H13" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 13.352px</v>
+      </c>
+      <c r="I13" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>1m 12.424px</v>
+      </c>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="M13" s="6">
+        <v>1.7765</v>
+      </c>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 7.52px</v>
+      </c>
+      <c r="F14" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 8.52px</v>
+      </c>
+      <c r="G14" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 13.6px</v>
+      </c>
+      <c r="H14" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 14.6px</v>
+      </c>
+      <c r="I14" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>1m 8.32px</v>
+      </c>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="M14" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 12.48px</v>
+      </c>
+      <c r="F15" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 13.48px</v>
+      </c>
+      <c r="G15" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 2.56px</v>
+      </c>
+      <c r="H15" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 3.56px</v>
+      </c>
+      <c r="I15" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>1m 7.12px</v>
+      </c>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="M15" s="6">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>11</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>3m 0.719999999999999px</v>
+      </c>
+      <c r="F16" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>3m 1.72px</v>
+      </c>
+      <c r="G16" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 6.8px</v>
+      </c>
+      <c r="H16" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 7.8px</v>
+      </c>
+      <c r="I16" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>2m 4.4px</v>
+      </c>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6">
+        <v>1.425</v>
+      </c>
+      <c r="M16" s="6">
+        <v>2.2749999999999999</v>
+      </c>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 1.36px</v>
+      </c>
+      <c r="F17" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 2.36px</v>
+      </c>
+      <c r="G17" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 7.44px</v>
+      </c>
+      <c r="H17" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 8.44px</v>
+      </c>
+      <c r="I17" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>0m 14.48px</v>
+      </c>
+      <c r="J17" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M17" s="6">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 4.56px</v>
+      </c>
+      <c r="F18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 5.56px</v>
+      </c>
+      <c r="G18" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 10.64px</v>
+      </c>
+      <c r="H18" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 11.64px</v>
+      </c>
+      <c r="I18" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>1m 9.04px</v>
+      </c>
+      <c r="J18" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="M18" s="6">
+        <v>1.425</v>
+      </c>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 5.76000000000001px</v>
+      </c>
+      <c r="F19" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 6.76000000000001px</v>
+      </c>
+      <c r="G19" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 11.84px</v>
+      </c>
+      <c r="H19" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 12.84px</v>
+      </c>
+      <c r="I19" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>1m 10.56px</v>
+      </c>
+      <c r="J19" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="M19" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 6.76000000000001px</v>
+      </c>
+      <c r="F20" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 7.76000000000001px</v>
+      </c>
+      <c r="G20" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 12.84px</v>
+      </c>
+      <c r="H20" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 13.84px</v>
+      </c>
+      <c r="I20" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>1m 10.56px</v>
+      </c>
+      <c r="J20" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6">
+        <v>0.66249999999999998</v>
+      </c>
+      <c r="M20" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 8.512px</v>
+      </c>
+      <c r="F21" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 9.512px</v>
+      </c>
+      <c r="G21" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 14.592px</v>
+      </c>
+      <c r="H21" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 15.592px</v>
+      </c>
+      <c r="I21" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>1m 14.664px</v>
+      </c>
+      <c r="J21" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="M21" s="6">
+        <v>1.7765</v>
+      </c>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 9.76000000000001px</v>
+      </c>
+      <c r="F22" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 10.76px</v>
+      </c>
+      <c r="G22" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 15.84px</v>
+      </c>
+      <c r="H22" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 0.84px</v>
+      </c>
+      <c r="I22" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>1m 10.56px</v>
+      </c>
+      <c r="J22" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="M22" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 14.72px</v>
+      </c>
+      <c r="F23" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 15.72px</v>
+      </c>
+      <c r="G23" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 4.8px</v>
+      </c>
+      <c r="H23" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 5.8px</v>
+      </c>
+      <c r="I23" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>1m 9.36px</v>
+      </c>
+      <c r="J23" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="M23" s="6">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>3m 2.96px</v>
+      </c>
+      <c r="F24" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>3m 3.96px</v>
+      </c>
+      <c r="G24" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 9.04px</v>
+      </c>
+      <c r="H24" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 10.04px</v>
+      </c>
+      <c r="I24" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>2m 6.64px</v>
+      </c>
+      <c r="J24" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6">
+        <v>1.425</v>
+      </c>
+      <c r="M24" s="6">
+        <v>2.2749999999999999</v>
+      </c>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <v>22</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E25" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 1.36px</v>
+      </c>
+      <c r="F25" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 2.36px</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 7.44px</v>
+      </c>
+      <c r="H25" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 8.44px</v>
+      </c>
+      <c r="I25" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>0m 14.48px</v>
+      </c>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L25" s="6">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M25" s="6">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>23</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 8.512px</v>
+      </c>
+      <c r="F26" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 9.512px</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 14.592px</v>
+      </c>
+      <c r="H26" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 15.592px</v>
+      </c>
+      <c r="I26" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>1m 14.664px</v>
+      </c>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L26" s="6">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="M26" s="6">
+        <v>1.7765</v>
+      </c>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>24</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 14.72px</v>
+      </c>
+      <c r="F27" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 15.72px</v>
+      </c>
+      <c r="G27" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 4.8px</v>
+      </c>
+      <c r="H27" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 5.8px</v>
+      </c>
+      <c r="I27" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>1m 9.36px</v>
+      </c>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L27" s="6">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="M27" s="6">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>25</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 5.36px</v>
+      </c>
+      <c r="F28" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 6.36px</v>
+      </c>
+      <c r="G28" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 11.44px</v>
+      </c>
+      <c r="H28" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 12.44px</v>
+      </c>
+      <c r="I28" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>1m 2.48px</v>
+      </c>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="L28" s="6">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M28" s="6">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>26</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 12.512px</v>
+      </c>
+      <c r="F29" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 13.512px</v>
+      </c>
+      <c r="G29" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 2.592px</v>
+      </c>
+      <c r="H29" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 3.592px</v>
+      </c>
+      <c r="I29" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>2m 2.664px</v>
+      </c>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="L29" s="6">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="M29" s="6">
+        <v>1.7765</v>
+      </c>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <v>27</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>3m 2.72px</v>
+      </c>
+      <c r="F30" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>3m 3.72px</v>
+      </c>
+      <c r="G30" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 8.8px</v>
+      </c>
+      <c r="H30" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 9.8px</v>
+      </c>
+      <c r="I30" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>1m 13.36px</v>
+      </c>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="L30" s="6">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="M30" s="6">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 1.36px</v>
+      </c>
+      <c r="F31" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 2.36px</v>
+      </c>
+      <c r="G31" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 7.44px</v>
+      </c>
+      <c r="H31" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 8.44px</v>
+      </c>
+      <c r="I31" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>0m 14.48px</v>
+      </c>
+      <c r="J31" s="6">
+        <v>0</v>
+      </c>
+      <c r="K31" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L31" s="6">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M31" s="6">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <v>29</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 8.512px</v>
+      </c>
+      <c r="F32" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 9.512px</v>
+      </c>
+      <c r="G32" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 14.592px</v>
+      </c>
+      <c r="H32" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 15.592px</v>
+      </c>
+      <c r="I32" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>1m 14.664px</v>
+      </c>
+      <c r="J32" s="6">
+        <v>0</v>
+      </c>
+      <c r="K32" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L32" s="6">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="M32" s="6">
+        <v>1.7765</v>
+      </c>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <v>30</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 14.72px</v>
+      </c>
+      <c r="F33" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 15.72px</v>
+      </c>
+      <c r="G33" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 4.8px</v>
+      </c>
+      <c r="H33" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 5.8px</v>
+      </c>
+      <c r="I33" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>1m 9.36px</v>
+      </c>
+      <c r="J33" s="6">
+        <v>0</v>
+      </c>
+      <c r="K33" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L33" s="6">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="M33" s="6">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <v>31</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E34" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 5.36px</v>
+      </c>
+      <c r="F34" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 6.36px</v>
+      </c>
+      <c r="G34" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>0m 11.44px</v>
+      </c>
+      <c r="H34" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>0m 12.44px</v>
+      </c>
+      <c r="I34" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>1m 2.48px</v>
+      </c>
+      <c r="J34" s="6">
+        <v>0</v>
+      </c>
+      <c r="K34" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="L34" s="6">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M34" s="6">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <v>32</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>2m 12.512px</v>
+      </c>
+      <c r="F35" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2m 13.512px</v>
+      </c>
+      <c r="G35" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 2.592px</v>
+      </c>
+      <c r="H35" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 3.592px</v>
+      </c>
+      <c r="I35" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>2m 2.664px</v>
+      </c>
+      <c r="J35" s="6">
+        <v>0</v>
+      </c>
+      <c r="K35" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="L35" s="6">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="M35" s="6">
+        <v>1.7765</v>
+      </c>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <v>33</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>3m 2.72px</v>
+      </c>
+      <c r="F36" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>3m 3.72px</v>
+      </c>
+      <c r="G36" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>1m 8.8px</v>
+      </c>
+      <c r="H36" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>1m 9.8px</v>
+      </c>
+      <c r="I36" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>1m 13.36px</v>
+      </c>
+      <c r="J36" s="6">
+        <v>0</v>
+      </c>
+      <c r="K36" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="L36" s="6">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="M36" s="6">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="J1:M1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3807DD25-8EFF-4D65-BFF6-A690D0D26684}">
   <dimension ref="A1:O36"/>
   <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -2955,25 +6361,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="13" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
       <c r="I1" s="8"/>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
     </row>
@@ -4433,15 +7839,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.58203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.9140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.58203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.58203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="8.9140625" style="2"/>
   </cols>
   <sheetData>
@@ -4768,15 +8174,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEB9D88C-9594-4ED7-93DA-80DA60D28A9A}">
   <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
